--- a/data/processed/companies.xlsx
+++ b/data/processed/companies.xlsx
@@ -413,855 +413,848 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>mkt_fintech_—_nifty_100__|__companies__|__92_records</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>unnamed:_1</t>
+          <t>company_logo</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>unnamed:_2</t>
+          <t>company_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>unnamed:_3</t>
+          <t>chart_link</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>unnamed:_4</t>
+          <t>about_company</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>unnamed:_5</t>
+          <t>website</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>unnamed:_6</t>
+          <t>nse_profile</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>unnamed:_7</t>
+          <t>bse_profile</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>unnamed:_8</t>
+          <t>face_value</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>unnamed:_9</t>
+          <t>book_value</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>unnamed:_10</t>
+          <t>roce_percentage</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>unnamed:_11</t>
+          <t>roe_percentage</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>company_logo</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/ABB.png</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>company_name</t>
+          <t>Abbott India Ltd</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>chart_link</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AABBOTINDIA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>about_company</t>
+          <t>Abbott India Ltd is one of the leading multinational pharmaceutical companies in India and sells its products through independent distributors primarily within India.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>https://www.abbott.co.in/</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nse_profile</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=ABBOTINDIA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>bse_profile</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>face_value</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>book_value</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>roce_percentage</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>roe_percentage</t>
-        </is>
+          <t>https://www.bseindia.com/stock-share-price/abbott-india-ltd/ABBOTINDIA/500488/</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1657</v>
+      </c>
+      <c r="K2" t="n">
+        <v>46</v>
+      </c>
+      <c r="L2" t="n">
+        <v>34.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/ABB.png</t>
+          <t>https://m.economictimes.com/thumb/msid-117371599,width-1200,height-900,resizemode-4,imgsize-5642/the-growth-story-remains-intact-for-adani-energy-solutions-says-jefferies.jpg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Abbott India Ltd</t>
+          <t>Adani Energy Solutions Ltd</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AABBOTINDIA</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AADANIENSOL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Abbott India Ltd is one of the leading multinational pharmaceutical companies in India and sells its products through independent distributors primarily within India.</t>
+          <t>AESL, part of the Adani portfolio, is a multidimensional organization with presence in various facets of the energy domain, namely power transmission, distribution, smart metering, and cooling solutions. AESL is India's largest private transmission company</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.abbott.co.in/</t>
+          <t>https://www.adanienergysolutions.com/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=ABBOTINDIA</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=ADANIENSOL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/abbott-india-ltd/ABBOTINDIA/500488/</t>
+          <t>https://www.bseindia.com/stock-share-price/adani-energy-solutions-ltd/ADANIENSOL/539254/</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>1657</v>
+        <v>175</v>
       </c>
       <c r="K3" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="L3" t="n">
-        <v>34.9</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/thumb/msid-117371599,width-1200,height-900,resizemode-4,imgsize-5642/the-growth-story-remains-intact-for-adani-energy-solutions-says-jefferies.jpg</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/ADANIENT.png</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Adani Energy Solutions Ltd</t>
+          <t>Adani Enterprises Ltd</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AADANIENSOL</t>
+          <t>https://in.tradingview.com/chart/?symbol=ADANIENT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AESL, part of the Adani portfolio, is a multidimensional organization with presence in various facets of the energy domain, namely power transmission, distribution, smart metering, and cooling solutions. AESL is India's largest private transmission company</t>
+          <t>Adani Enterprises Ltd is an Indian multinational public company and a subsidiary of Adani Group. It is headquartered in Ahmedabad and has business interests in coal mining and trading, airport operations, edible oils, road, rail and water infrastructure, data centers, hydrocarbon exploration, defence and aerospace, multimodal logistics, and agro commodities.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.adanienergysolutions.com/</t>
+          <t>https://www.adanienterprises.com/</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=ADANIENSOL</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=ADANIENT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/adani-energy-solutions-ltd/ADANIENSOL/539254/</t>
+          <t>https://www.bseindia.com/stock-share-price/adani-enterprises-ltd/adanient/512</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>175</v>
+        <v>363</v>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>11.6</v>
       </c>
       <c r="L4" t="n">
-        <v>8.59</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/ADANIENT.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/ADANIGREEN.png</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Adani Enterprises Ltd</t>
+          <t>Adani Green Energy Ltd</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=ADANIENT</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AADANIGREEN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Adani Enterprises Ltd is an Indian multinational public company and a subsidiary of Adani Group. It is headquartered in Ahmedabad and has business interests in coal mining and trading, airport operations, edible oils, road, rail and water infrastructure, data centers, hydrocarbon exploration, defence and aerospace, multimodal logistics, and agro commodities.</t>
+          <t>Adani Green Energy Limited, incorporated in 2015, is a holding company of several subsidiaries carrying business of renewable power generation within the group and is primarily involved in renewable power generation and other ancillary activities.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.adanienterprises.com/</t>
+          <t>http://www.adanigreenenergy.com/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=ADANIENT</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=ADANIGREEN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/adani-enterprises-ltd/adanient/512</t>
+          <t>https://www.bseindia.com/stock-share-price/adani-green-energy-ltd/ADANIGREEN/541450/</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>363</v>
+        <v>67</v>
       </c>
       <c r="K5" t="n">
-        <v>11.6</v>
+        <v>96.5</v>
       </c>
       <c r="L5" t="n">
-        <v>13.64</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/ADANIGREEN.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/ADANIPORTS.png</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Adani Green Energy Ltd</t>
+          <t xml:space="preserve">Adani Ports &amp; Special Economic Zone Ltd
+</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AADANIGREEN</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AADANIPORTS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Adani Green Energy Limited, incorporated in 2015, is a holding company of several subsidiaries carrying business of renewable power generation within the group and is primarily involved in renewable power generation and other ancillary activities.</t>
+          <t>Adani Ports &amp; Special Economic Zone is in the business of development, operations and maintenance of port infrastructure (port services and related infrastructure development) and has linked multi product Special Economic Zone (SEZ) and related infrastructure contiguous to Port at Mundra.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>http://www.adanigreenenergy.com/</t>
+          <t>http://www.adaniports.com/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=ADANIGREEN</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=ADANIPORTS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/adani-green-energy-ltd/ADANIGREEN/541450/</t>
+          <t>https://www.bseindia.com/stock-share-price/adani-ports-special-economic-zone-ltd/ADANIPORTS/532921/</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>67</v>
+        <v>265</v>
       </c>
       <c r="K6" t="n">
-        <v>96.5</v>
+        <v>12.9</v>
       </c>
       <c r="L6" t="n">
-        <v>14.7</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/ADANIPORTS.png</t>
+          <t xml:space="preserve">https://mkt.in/static/mkt-icons/nifty100/ADANIPOWER.png
+</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adani Ports &amp; Special Economic Zone Ltd
-</t>
+          <t>Adani Power Ltd</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AADANIPORTS</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AADANIPOWER</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Adani Ports &amp; Special Economic Zone is in the business of development, operations and maintenance of port infrastructure (port services and related infrastructure development) and has linked multi product Special Economic Zone (SEZ) and related infrastructure contiguous to Port at Mundra.</t>
+          <t>Adani Power (APL), a part of the diversified Adani Group, is the largest private thermal power producer in India. The co along with its subsidiaries sell power generated from these projects under a combination of long term Power Purchase Agreements, Short term PPA and on merchant basis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>http://www.adaniports.com/</t>
+          <t>http://www.adani.com/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=ADANIPORTS</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=ADANIPOWER</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/adani-ports-special-economic-zone-ltd/ADANIPORTS/532921/</t>
+          <t>https://www.bseindia.com/stock-share-price/adani-power-ltd/ADANIPOWER/533096/</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>265</v>
+        <v>145</v>
       </c>
       <c r="K7" t="n">
-        <v>12.9</v>
+        <v>32.2</v>
       </c>
       <c r="L7" t="n">
-        <v>18.1</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://mkt.in/static/mkt-icons/nifty100/ADANIPOWER.png
-</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/AMBUJACEM.png</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Adani Power Ltd</t>
+          <t>Ambuja Cements Ltd</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AADANIPOWER</t>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Adani Power (APL), a part of the diversified Adani Group, is the largest private thermal power producer in India. The co along with its subsidiaries sell power generated from these projects under a combination of long term Power Purchase Agreements, Short term PPA and on merchant basis</t>
+          <t>Ambuja Cements Ltd. is among the leading cement companies in India. It is a member of the Adani Group. Currently, Ambuja Cement has a cement capacity of 31 million tonnes with six integrated cement manufacturing plants</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>http://www.adani.com/</t>
+          <t>https://www.ambujacement.com/</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=ADANIPOWER</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=AMBUJACEM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/adani-power-ltd/ADANIPOWER/533096/</t>
+          <t>https://www.bseindia.com/stock-share-price/ambuja-cements-ltd/AMBUJACEM/500425/</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="K8" t="n">
-        <v>32.2</v>
+        <v>12.8</v>
       </c>
       <c r="L8" t="n">
-        <v>57.1</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/AMBUJACEM.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/APOLLOHOSP.png</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ambuja Cements Ltd</t>
+          <t>Apollo Hospitals
+Chain of Indian private hospitals</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AAPOLLOHOSP</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ambuja Cements Ltd. is among the leading cement companies in India. It is a member of the Adani Group. Currently, Ambuja Cement has a cement capacity of 31 million tonnes with six integrated cement manufacturing plants</t>
+          <t>Apollo Hospitals Enterprise Limited is an Indian multinational healthcare group headquartered in Chennai. It is the largest for-profit private hospital network in India, with a network of 71 owned and managed hospitals.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.ambujacement.com/</t>
+          <t>https://www.apollohospitals.com/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=AMBUJACEM</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=APOLLOHOSP</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/ambuja-cements-ltd/AMBUJACEM/500425/</t>
+          <t>https://www.bseindia.com/stock-share-price/apollo-hospitals-enterprise-ltd/apollohosp/508869/</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>205</v>
+        <v>522</v>
       </c>
       <c r="K9" t="n">
-        <v>12.8</v>
+        <v>17.2</v>
       </c>
       <c r="L9" t="n">
-        <v>9.24</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/APOLLOHOSP.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/ASIANPAINT.png</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Apollo Hospitals
-Chain of Indian private hospitals</t>
+          <t>Asian Paints
+Indian Multi-National Paint and Coating Manufacturing Company</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AAPOLLOHOSP</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AASIANPAINT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Limited is an Indian multinational healthcare group headquartered in Chennai. It is the largest for-profit private hospital network in India, with a network of 71 owned and managed hospitals.</t>
+          <t>Asian Paints Ltd is an Indian multinational paint company, headquartered in Mumbai. The company is engaged in the business of manufacturing, selling and distribution of paints, coatings, products related to home decor, bath fittings and providing related services.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.apollohospitals.com/</t>
+          <t>https://www.asianpaints.com/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=APOLLOHOSP</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=ASIANPAINT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/apollo-hospitals-enterprise-ltd/apollohosp/508869/</t>
+          <t>https://www.bseindia.com/stock-share-price/asian-paints-ltd/asianpaint/500820/</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>522</v>
+        <v>188</v>
       </c>
       <c r="K10" t="n">
-        <v>17.2</v>
+        <v>41.75</v>
       </c>
       <c r="L10" t="n">
-        <v>13.81</v>
+        <v>31.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/ASIANPAINT.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/ATGL.png</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Asian Paints
-Indian Multi-National Paint and Coating Manufacturing Company</t>
+          <t>Adani Total Gas Ltd</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AASIANPAINT</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AATGL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Asian Paints Ltd is an Indian multinational paint company, headquartered in Mumbai. The company is engaged in the business of manufacturing, selling and distribution of paints, coatings, products related to home decor, bath fittings and providing related services.</t>
+          <t>AGL is engaged in City Gas Distribution (CGD) business and supplies natural gas to domestic, commercial, industrial and vehicle users.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.asianpaints.com/</t>
+          <t>http://www.adanigas.com/</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=ASIANPAINT</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=ATGL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/asian-paints-ltd/asianpaint/500820/</t>
+          <t>https://www.bseindia.com/stock-share-price/adani-total-gas-ltd/ATGL/542066/</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>188</v>
+        <v>36</v>
       </c>
       <c r="K11" t="n">
-        <v>41.75</v>
+        <v>21.2</v>
       </c>
       <c r="L11" t="n">
-        <v>31.45</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/ATGL.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/AXISBANK.png</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Adani Total Gas Ltd</t>
+          <t>Axis Bank Ltd</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AATGL</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AAXISBANK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AGL is engaged in City Gas Distribution (CGD) business and supplies natural gas to domestic, commercial, industrial and vehicle users.</t>
+          <t>Incorporated in December 1993, Axis Bank Limited is a private sector bank.It has the third-largest network of branches among private sector banks and an international presence through branches in DIFC (Dubai) and Singapore along with representative offices in Abu Dhabi, Sharjah, Dhaka and Dubai and an offshore banking unit in GIFT City.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>http://www.adanigas.com/</t>
+          <t>http://www.axisbank.com/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=ATGL</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=AXISBANK</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/adani-total-gas-ltd/ATGL/542066/</t>
+          <t>https://www.bseindia.com/stock-share-price/axis-bank-ltd/AXISBANK/532215/</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>36</v>
+        <v>509</v>
       </c>
       <c r="K12" t="n">
-        <v>21.2</v>
+        <v>7.06</v>
       </c>
       <c r="L12" t="n">
-        <v>20.5</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/AXISBANK.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/BAJAJ-AUTO.png</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd</t>
+          <t>Bajaj Auto Ltd</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AAXISBANK</t>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>Incorporated in December 1993, Axis Bank Limited is a private sector bank.It has the third-largest network of branches among private sector banks and an international presence through branches in DIFC (Dubai) and Singapore along with representative offices in Abu Dhabi, Sharjah, Dhaka and Dubai and an offshore banking unit in GIFT City.</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>http://www.axisbank.com/</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=AXISBANK</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.bseindia.com/stock-share-price/axis-bank-ltd/AXISBANK/532215/</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>509</v>
-      </c>
-      <c r="K13" t="n">
-        <v>7.06</v>
-      </c>
-      <c r="L13" t="n">
-        <v>18.4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/BAJAJ-AUTO.png</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bajaj Auto Ltd</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
         <is>
           <t xml:space="preserve">Bajaj Auto, the flagship company of Bajaj Group, is a two-wheeler and three-wheeler manufacturing company that exports to 79 countries across several countries in Latin America, Southeast Asia, and many more. Its headquarter is in Pune, India.
 It has acquired 48% of the KTM Brand which manufactures sports and super sports two-wheelers, which was 14% in 2007 when the company first acquired KTM. [1]
 </t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.bajajauto.com/</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.bseindia.com/stock-share-price/bajaj-auto-ltd/BAJAJ-AUTO/532977/</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1109</v>
+      </c>
+      <c r="K13" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://mkt.in/static/mkt-icons/nifty100/BAJAJFINSV.png</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bajaj Finserv Ltd</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3ABAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Bajaj Finserv Limited is an Indian non-banking financial services company headquartered in Pune. It is focused on lending, asset management, wealth management and insurance.</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.bajajauto.com/</t>
+          <t>https://www.bajajfinserv.in/</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=BAJAJ-AUTO</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=BAJAJFINSV</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/bajaj-auto-ltd/BAJAJ-AUTO/532977/</t>
+          <t>https://www.bseindia.com/stock-share-price/bajaj-finserv-ltd/bajajfinsv/532978/</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>1109</v>
+        <v>428</v>
       </c>
       <c r="K14" t="n">
-        <v>33.5</v>
+        <v>21.14</v>
       </c>
       <c r="L14" t="n">
-        <v>26.5</v>
+        <v>11.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/BAJAJFINSV.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/BAJAJHLDNG.png</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Ltd</t>
+          <t>Bajaj Holdings &amp; Investment Ltd</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3ABAJAJFINSV</t>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Limited is an Indian non-banking financial services company headquartered in Pune. It is focused on lending, asset management, wealth management and insurance.</t>
+          <t xml:space="preserve">Bajaj Holdings &amp; Investment Ltd. operates as an Investment Company and is registered as a Non-Banking Financial Institution- Investment and Credit Company with the Reserve Bank of India. The Co. holds more than 36% stake in both Bajaj Auto Ltd. and Bajaj Finserv Ltd.
+</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.bajajfinserv.in/</t>
+          <t>https://www.bhil.in/</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=BAJAJFINSV</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=BAJAJHLDNG</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/bajaj-finserv-ltd/bajajfinsv/532978/</t>
+          <t>https://www.bseindia.com/stock-share-price/bajaj-holdings-investment-ltd/BAJAJHLDNG/500490/</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>428</v>
+        <v>5375</v>
       </c>
       <c r="K15" t="n">
-        <v>21.14</v>
+        <v>13.1</v>
       </c>
       <c r="L15" t="n">
-        <v>11.72</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/BAJAJHLDNG.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/BAJFINANCE.png</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bajaj Holdings &amp; Investment Ltd</t>
+          <t>Bajaj Finance Ltd</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1271,324 +1264,323 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bajaj Holdings &amp; Investment Ltd. operates as an Investment Company and is registered as a Non-Banking Financial Institution- Investment and Credit Company with the Reserve Bank of India. The Co. holds more than 36% stake in both Bajaj Auto Ltd. and Bajaj Finserv Ltd.
-</t>
+          <t>Bajaj Finance is mainly engaged in the business of lending. BFL has a diversified lending portfolio across retail, SME and commercial customers with a significant presence in urban and rural India. It also accepts public and corporate deposits and offers variety of financial services products to its customers.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.bhil.in/</t>
+          <t>https://www.bajajfinserv.in/</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=BAJAJHLDNG</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=BAJFINANCE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/bajaj-holdings-investment-ltd/BAJAJHLDNG/500490/</t>
+          <t>https://www.bseindia.com/stock-share-price/bajaj-finance-ltd/BAJFINANCE/500034/</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>5375</v>
+        <v>1402</v>
       </c>
       <c r="K16" t="n">
-        <v>13.1</v>
+        <v>11.9</v>
       </c>
       <c r="L16" t="n">
-        <v>14.8</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/BAJFINANCE.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/BANKBARODA.png</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bajaj Finance Ltd</t>
+          <t>Bank of Baroda</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
+          <t>https://in.tradingview.com/chart/?symbol=BANKBARODA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bajaj Finance is mainly engaged in the business of lending. BFL has a diversified lending portfolio across retail, SME and commercial customers with a significant presence in urban and rural India. It also accepts public and corporate deposits and offers variety of financial services products to its customers.</t>
+          <t>Bank of Baroda is engaged in providing various services, such as personal banking, corporate banking, international banking, small and medium enterprise (SME) banking, rural banking, non-resident Indian (NRI) services and treasury services.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.bajajfinserv.in/</t>
+          <t>http://www.bankofbaroda.co.in/</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=BAJFINANCE</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=BANKBARODA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/bajaj-finance-ltd/BAJFINANCE/500034/</t>
+          <t>https://www.bseindia.com/stock-share-price/bank-of-baroda/BANKBARODA/532134/</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>1402</v>
+        <v>231</v>
       </c>
       <c r="K17" t="n">
-        <v>11.9</v>
+        <v>6.33</v>
       </c>
       <c r="L17" t="n">
-        <v>22.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/BANKBARODA.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/BEL.png</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bank of Baroda</t>
+          <t>Bharat Electronics Ltd</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=BANKBARODA</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3ABEL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bank of Baroda is engaged in providing various services, such as personal banking, corporate banking, international banking, small and medium enterprise (SME) banking, rural banking, non-resident Indian (NRI) services and treasury services.</t>
+          <t>Incorporated in 1954, Bharat Electronics Ltd manufactures and supplies electronic equipment and systems to the defence sector. Company also has a limited presence in the civilian market</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>http://www.bankofbaroda.co.in/</t>
+          <t>http://www.bel-india.in/</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=BANKBARODA</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=BEL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/bank-of-baroda/BANKBARODA/532134/</t>
+          <t>https://www.bseindia.com/stock-share-price/bharat-electronics-ltd/BEL/500049/</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>231</v>
+        <v>24</v>
       </c>
       <c r="K18" t="n">
-        <v>6.33</v>
+        <v>34.6</v>
       </c>
       <c r="L18" t="n">
-        <v>16.7</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/BEL.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/BHARTIARTL.png</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd</t>
+          <t>Bharti Airtel Ltd</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3ABEL</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3ABHARTIARTL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Incorporated in 1954, Bharat Electronics Ltd manufactures and supplies electronic equipment and systems to the defence sector. Company also has a limited presence in the civilian market</t>
+          <t>Bharti Airtel Ltd is one of the world's leading providers of telecommunication services with presence in 18 countries representing India, Sri
+Lanka, 14 countries in Africa.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>http://www.bel-india.in/</t>
+          <t>http://www.airtel.in/</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=BEL</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=BHARTIARTL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/bharat-electronics-ltd/BEL/500049/</t>
+          <t>https://www.bseindia.com/stock-share-price/bharti-airtel-ltd/BHARTIARTL/532454/</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="K19" t="n">
-        <v>34.6</v>
+        <v>13.1</v>
       </c>
       <c r="L19" t="n">
-        <v>26.3</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/BHARTIARTL.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/BHEL.png</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bharti Airtel Ltd</t>
+          <t xml:space="preserve">Bharat Heavy Electricals Limited
+</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3ABHARTIARTL</t>
+          <t>https://in.tradingview.com/chart/?symbol=BSE%3ABHEL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bharti Airtel Ltd is one of the world's leading providers of telecommunication services with presence in 18 countries representing India, Sri
-Lanka, 14 countries in Africa.</t>
+          <t>Bharat Heavy Electricals Limited is an Indian central public sector undertaking and the largest government-owned electrical/ industrial technology company.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>http://www.airtel.in/</t>
+          <t>https://www.bhel.com/</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=BHARTIARTL</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=BHEL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/bharti-airtel-ltd/BHARTIARTL/532454/</t>
+          <t>https://www.bseindia.com/stock-share-price/bharat-electronics-ltd/bel/500049/</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>153</v>
+        <v>70</v>
       </c>
       <c r="K20" t="n">
-        <v>13.1</v>
+        <v>3.28</v>
       </c>
       <c r="L20" t="n">
-        <v>14.9</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/BHEL.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/BOSCHLTD.png</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bharat Heavy Electricals Limited
-</t>
+          <t>Bosch Ltd</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=BSE%3ABHEL</t>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Limited is an Indian central public sector undertaking and the largest government-owned electrical/ industrial technology company.</t>
+          <t>Bosch Ltd has presence across automotive technology, industrial technology, consumer goods and energy and building technology. It manufactures and trades in products such as diesel and gasoline fuel injection systems, automotive aftermarket products, industrial equipment, electrical power tools, security systems</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.bhel.com/</t>
+          <t>https://www.bosch.in/</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=BHEL</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=BOSCHLTD</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/bharat-electronics-ltd/bel/500049/</t>
+          <t>https://www.bseindia.com/stock-share-price/bosch-ltd/BOSCHLTD/500530/</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>70</v>
+        <v>4319</v>
       </c>
       <c r="K21" t="n">
-        <v>3.28</v>
+        <v>20.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.05</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/BOSCHLTD.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/BPCL.png</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bosch Ltd</t>
+          <t>Bharat Petroleum Corporation Ltd</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1598,51 +1590,52 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bosch Ltd has presence across automotive technology, industrial technology, consumer goods and energy and building technology. It manufactures and trades in products such as diesel and gasoline fuel injection systems, automotive aftermarket products, industrial equipment, electrical power tools, security systems</t>
+          <t xml:space="preserve">Bharat Petroleum Corporation is a public sector company which is engaged in the business of refining of crude oil and marketing of petroleum products.[1]
+</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.bosch.in/</t>
+          <t>https://www.bharatpetroleum.in/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=BOSCHLTD</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=BPCL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/bosch-ltd/BOSCHLTD/500530/</t>
+          <t>https://www.bseindia.com/stock-share-price/bharat-petroleum-corporation-ltd/BPCL/500547/</t>
         </is>
       </c>
       <c r="I22" t="n">
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>4319</v>
+        <v>178</v>
       </c>
       <c r="K22" t="n">
-        <v>20.6</v>
+        <v>32.1</v>
       </c>
       <c r="L22" t="n">
-        <v>16</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/BPCL.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/BRITANNIA.png</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bharat Petroleum Corporation Ltd</t>
+          <t>Britannia Industries Ltd</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1652,380 +1645,379 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bharat Petroleum Corporation is a public sector company which is engaged in the business of refining of crude oil and marketing of petroleum products.[1]
+          <t xml:space="preserve">Britannia Industries is one of Indias leading food companies with a 100 year legacy and annual revenues in excess of Rs. 9000 Cr. Britannia is among the most trusted food brands, and manufactures Indias favorite brands like Good Day, Tiger, NutriChoice, Milk Bikis and Marie Gold which are household names in India. Britannias product portfolio includes Biscuits, Bread, Cakes, Rusk, and Dairy products including Cheese, Beverages, Milk and Yoghurt.
 </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.bharatpetroleum.in/</t>
+          <t>https://www.britannia.co.in/</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=BPCL</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=BRITANNIA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/bharat-petroleum-corporation-ltd/BPCL/500547/</t>
+          <t>https://www.bseindia.com/stock-share-price/britannia-industries-ltd/BRITANNIA/500825/</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="K23" t="n">
-        <v>32.1</v>
+        <v>48.9</v>
       </c>
       <c r="L23" t="n">
-        <v>41.9</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/BRITANNIA.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/CANBK.png</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Britannia Industries Ltd</t>
+          <t>Canara Bank</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3ACANBK</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britannia Industries is one of Indias leading food companies with a 100 year legacy and annual revenues in excess of Rs. 9000 Cr. Britannia is among the most trusted food brands, and manufactures Indias favorite brands like Good Day, Tiger, NutriChoice, Milk Bikis and Marie Gold which are household names in India. Britannias product portfolio includes Biscuits, Bread, Cakes, Rusk, and Dairy products including Cheese, Beverages, Milk and Yoghurt.
-</t>
+          <t>Canara Bank was merged with erstwhile Syndicate Bank in FY21.{# Canara was incorporated in 1906 and nationalised in 1969, along with 13 other major commercial banks of India, by the GoI. The bank is headquartered in Bangalore.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.britannia.co.in/</t>
+          <t>http://www.canarabank.com/</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=BRITANNIA</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=CANBK</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/britannia-industries-ltd/BRITANNIA/500825/</t>
+          <t>https://www.bseindia.com/stock-share-price/canara-bank/CANBK/532483/</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="K24" t="n">
-        <v>48.9</v>
+        <v>6.63</v>
       </c>
       <c r="L24" t="n">
-        <v>57.1</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/CANBK.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/CHOLAFIN.png</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Canara Bank</t>
+          <t>Cholamandalam Investment &amp; Finance Company Ltd</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3ACANBK</t>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Canara Bank was merged with erstwhile Syndicate Bank in FY21.{# Canara was incorporated in 1906 and nationalised in 1969, along with 13 other major commercial banks of India, by the GoI. The bank is headquartered in Bangalore.</t>
+          <t xml:space="preserve">Cholamandalam Investment &amp; Finance Company is one of the premier diversified non-banking finance companies in India, engaged in providing vehicle finance, home loans and Loan against property.[1]
+</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>http://www.canarabank.com/</t>
+          <t>https://www.cholamandalam.com/</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=CANBK</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=CHOLAFIN</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/canara-bank/CANBK/532483/</t>
+          <t>https://www.bseindia.com/stock-share-price/cholamandalam-investment-finance-company-ltd/CHOLAFIN/511243/</t>
         </is>
       </c>
       <c r="I25" t="n">
         <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>102</v>
+        <v>255</v>
       </c>
       <c r="K25" t="n">
-        <v>6.63</v>
+        <v>10.4</v>
       </c>
       <c r="L25" t="n">
-        <v>17.9</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/CHOLAFIN.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/CIPLA.png</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cholamandalam Investment &amp; Finance Company Ltd</t>
+          <t xml:space="preserve">Cipla Ltd
+</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
+          <t xml:space="preserve">https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0
+</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cholamandalam Investment &amp; Finance Company is one of the premier diversified non-banking finance companies in India, engaged in providing vehicle finance, home loans and Loan against property.[1]
-</t>
+          <t>Cipla is engaged in the Business of Pharmaceuticals.(Source : 202003 Annual Report Page No:157)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.cholamandalam.com/</t>
+          <t>https://www.cipla.com/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=CHOLAFIN</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=CIPLA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/cholamandalam-investment-finance-company-ltd/CHOLAFIN/511243/</t>
+          <t>https://www.bseindia.com/stock-share-price/cipla-ltd/CIPLA/500087/</t>
         </is>
       </c>
       <c r="I26" t="n">
         <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>255</v>
+        <v>351</v>
       </c>
       <c r="K26" t="n">
-        <v>10.4</v>
+        <v>22.8</v>
       </c>
       <c r="L26" t="n">
-        <v>20.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/CIPLA.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/COALINDIA.png</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cipla Ltd
-</t>
+          <t>Coal India Ltd</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0
-</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3ACOALINDIA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cipla is engaged in the Business of Pharmaceuticals.(Source : 202003 Annual Report Page No:157)</t>
+          <t>Coal India Ltd is mainly engaged in mining and production of Coal and also operates Coal washeries. The major consumers of the company are power and steel sectors. Consumers from other sectors include cement, fertilizers, brick kilns etc.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.cipla.com/</t>
+          <t>http://www.coalindia.in/</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=CIPLA</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=COALINDIA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/cipla-ltd/CIPLA/500087/</t>
+          <t>https://www.bseindia.com/stock-share-price/coal-india-ltd/COALINDIA/533278/</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>351</v>
+        <v>156</v>
       </c>
       <c r="K27" t="n">
-        <v>22.8</v>
+        <v>63.6</v>
       </c>
       <c r="L27" t="n">
-        <v>16.8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/COALINDIA.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/DABUR.png</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Coal India Ltd</t>
+          <t>Dabur India Ltd</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3ACOALINDIA</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3ADABUR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coal India Ltd is mainly engaged in mining and production of Coal and also operates Coal washeries. The major consumers of the company are power and steel sectors. Consumers from other sectors include cement, fertilizers, brick kilns etc.</t>
+          <t>Dabur India is one of the leading fast moving consumer goods (FMCG) players dealing in consumer care and food products.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>http://www.coalindia.in/</t>
+          <t>http://www.dabur.com/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=COALINDIA</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=DABUR</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/coal-india-ltd/COALINDIA/533278/</t>
+          <t>https://www.bseindia.com/stock-share-price/dabur-india-ltd/DABUR/500096/</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>156</v>
+        <v>59</v>
       </c>
       <c r="K28" t="n">
-        <v>63.6</v>
+        <v>22.3</v>
       </c>
       <c r="L28" t="n">
-        <v>52</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/DABUR.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/DIVISLAB.png</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dabur India Ltd</t>
+          <t>Divis Laboratories Ltd</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3ADABUR</t>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dabur India is one of the leading fast moving consumer goods (FMCG) players dealing in consumer care and food products.</t>
+          <t>Incorporated in 1990, Divis Laboratories Ltd manufactures and exports API's, Intermediates and Nutraceutical ingredients</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>http://www.dabur.com/</t>
+          <t>https://www.divislaboratories.com/lander</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=DABUR</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=DIVISLAB</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/dabur-india-ltd/DABUR/500096/</t>
+          <t>https://www.bseindia.com/stock-share-price/divis-laboratories-ltd/DIVISLAB/532488/</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>59</v>
+        <v>517</v>
       </c>
       <c r="K29" t="n">
-        <v>22.3</v>
+        <v>16.5</v>
       </c>
       <c r="L29" t="n">
-        <v>19.2</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/DIVISLAB.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/DLF.png</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Divis Laboratories Ltd</t>
+          <t>DLF Ltd</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2035,160 +2027,160 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Incorporated in 1990, Divis Laboratories Ltd manufactures and exports API's, Intermediates and Nutraceutical ingredients</t>
+          <t>DLF Ltd with its subsidiaries, associates and JVs is engaged in real estate development, from the identification and acquisition of land to planning, execution, construction and marketing of projects. It is also engaged in business of leasing, generation of power, provision of maintenance services, hospitality and recreational services which are related to the overall development of real estate business.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.divislaboratories.com/lander</t>
+          <t>https://www.dlf.in/</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=DIVISLAB</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=DLF</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/divis-laboratories-ltd/DIVISLAB/532488/</t>
+          <t>https://www.bseindia.com/stock-share-price/dlf-ltd/DLF/532868/</t>
         </is>
       </c>
       <c r="I30" t="n">
         <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>517</v>
+        <v>163</v>
       </c>
       <c r="K30" t="n">
-        <v>16.5</v>
+        <v>5.74</v>
       </c>
       <c r="L30" t="n">
-        <v>12.2</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/DLF.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/DMART.png</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DLF Ltd</t>
+          <t>Avenue Supermarts Ltd</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3ADMART</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DLF Ltd with its subsidiaries, associates and JVs is engaged in real estate development, from the identification and acquisition of land to planning, execution, construction and marketing of projects. It is also engaged in business of leasing, generation of power, provision of maintenance services, hospitality and recreational services which are related to the overall development of real estate business.</t>
+          <t>Avenue Supermarts Limited (DMart) is a national supermarket chain, with a focus on value-retailing. We offer a wide range of products with a focus on the Foods, Non-Foods (FMCG) and General Merchandise
+&amp; Apparel product categories</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.dlf.in/</t>
+          <t>http://www.dmartindia.com/</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=DLF</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=DMART</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/dlf-ltd/DLF/532868/</t>
+          <t>https://www.bseindia.com/stock-share-price/avenue-supermarts-ltd/DMART/540376/</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="K31" t="n">
-        <v>5.74</v>
+        <v>19.4</v>
       </c>
       <c r="L31" t="n">
-        <v>6.95</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/DMART.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/DRREDDY.png</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Ltd</t>
+          <t>Dr Reddys Laboratories Ltd</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3ADMART</t>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Limited (DMart) is a national supermarket chain, with a focus on value-retailing. We offer a wide range of products with a focus on the Foods, Non-Foods (FMCG) and General Merchandise
-&amp; Apparel product categories</t>
+          <t>Dr. Reddy's Laboratories Ltd is a leading India-based pharmaceutical company which offers a portfolio of products and services, including Active Pharmaceutical Ingredients (APIs), Custom Pharmaceutical services (CPS), generics, biosimilars and differentiated formulations.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>http://www.dmartindia.com/</t>
+          <t>https://www.drreddys.com/</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=DMART</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=DRREDDY</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/avenue-supermarts-ltd/DMART/540376/</t>
+          <t>https://www.bseindia.com/stock-share-price/dr-reddys-laboratories-ltd/DRREDDY/500124/</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>309</v>
+        <v>369</v>
       </c>
       <c r="K32" t="n">
-        <v>19.4</v>
+        <v>26.5</v>
       </c>
       <c r="L32" t="n">
-        <v>14.5</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/DRREDDY.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/EICHERMOT.png</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd</t>
+          <t>Eicher Motors Ltd</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2198,214 +2190,214 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Ltd is a leading India-based pharmaceutical company which offers a portfolio of products and services, including Active Pharmaceutical Ingredients (APIs), Custom Pharmaceutical services (CPS), generics, biosimilars and differentiated formulations.</t>
+          <t xml:space="preserve">Eicher Motors Limited, incorporated in 1982, is the listed company of the Eicher Group in India and a leading player in the Indian automobile industry and the global leader in middleweight motorcycles.
+Eicher has a joint venture with Sweden's AB Volvo to create Volvo Eicher Commercial Vehicles Limited (VECV). VECV is engaged in truck and bus operations, auto components business, and technical </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.drreddys.com/</t>
+          <t>https://www.eicher.in/</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=DRREDDY</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=EICHERMOT</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/dr-reddys-laboratories-ltd/DRREDDY/500124/</t>
+          <t>https://www.bseindia.com/stock-share-price/eicher-motors-ltd/EICHERMOT/505200/</t>
         </is>
       </c>
       <c r="I33" t="n">
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>369</v>
+        <v>693</v>
       </c>
       <c r="K33" t="n">
-        <v>26.5</v>
+        <v>31.1</v>
       </c>
       <c r="L33" t="n">
-        <v>21.4</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/EICHERMOT.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/GAIL.png</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd</t>
+          <t>GAIL (India) Ltd</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AGAIL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eicher Motors Limited, incorporated in 1982, is the listed company of the Eicher Group in India and a leading player in the Indian automobile industry and the global leader in middleweight motorcycles.
-Eicher has a joint venture with Sweden's AB Volvo to create Volvo Eicher Commercial Vehicles Limited (VECV). VECV is engaged in truck and bus operations, auto components business, and technical </t>
+          <t>Incorporated in 1984, GAIL, a Government of India undertaking, is an integrated natural gas company in India. It owns over 11,500 km of natural gas pipelines, over 2300 km of LPG pipelines, six LPG gas-processing units and a petrochemicals facility. It also has a joint-venture interest in Petronet LNG Ltd, Ratnagiri Gas and Power Pvt Ltd, and in the CGD business in several cities</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.eicher.in/</t>
+          <t>https://gailonline.com/</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=EICHERMOT</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=GAIL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/eicher-motors-ltd/EICHERMOT/505200/</t>
+          <t>https://www.bseindia.com/stock-share-price/gail-india-ltd/GAIL/532155/</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>693</v>
+        <v>127</v>
       </c>
       <c r="K34" t="n">
-        <v>31.1</v>
+        <v>14.7</v>
       </c>
       <c r="L34" t="n">
-        <v>24.2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/GAIL.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/GODREJCP.png</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GAIL (India) Ltd</t>
+          <t>Godrej Consumer Products Ltd</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AGAIL</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AGODREJCP</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Incorporated in 1984, GAIL, a Government of India undertaking, is an integrated natural gas company in India. It owns over 11,500 km of natural gas pipelines, over 2300 km of LPG pipelines, six LPG gas-processing units and a petrochemicals facility. It also has a joint-venture interest in Petronet LNG Ltd, Ratnagiri Gas and Power Pvt Ltd, and in the CGD business in several cities</t>
+          <t>Godrej Consumer Products Limited is an Indian Multinational consumer goods company based in Mumbai, India. GCPL's products include soap, hair colourants, toiletries and liquid detergents.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://gailonline.com/</t>
+          <t>https://www.godrejcp.com/</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=GAIL</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=GODREJCP</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/gail-india-ltd/GAIL/532155/</t>
+          <t>https://www.bseindia.com/stock-share-price/godrej-consumer-products-ltd/godrejcp/532424/</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K35" t="n">
-        <v>14.7</v>
+        <v>26.49</v>
       </c>
       <c r="L35" t="n">
-        <v>14</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/GODREJCP.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/GRASIM.png</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Godrej Consumer Products Ltd</t>
+          <t>Grasim Industries Ltd</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AGODREJCP</t>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Godrej Consumer Products Limited is an Indian Multinational consumer goods company based in Mumbai, India. GCPL's products include soap, hair colourants, toiletries and liquid detergents.</t>
+          <t>Grasim Industries Limited is the flagship company of the Aditya Birla group, it ranks amongst India's largest private sector companies. On standalone basis, GIL's core businesses comprise of viscose Staple fibre (VSF), caustic soda, speciality chemicals, rayon-grade wood pulp (RGWP) with plants at multiple locations. It also has certain other businesses such as fertiliser, textile</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.godrejcp.com/</t>
+          <t>https://www.grasim.com/</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=GODREJCP</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=GRASIM</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/godrej-consumer-products-ltd/godrejcp/532424/</t>
+          <t>https://www.bseindia.com/stock-share-price/grasim-industries-ltd/GRASIM/500300/</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>119</v>
+        <v>1411</v>
       </c>
       <c r="K36" t="n">
-        <v>26.49</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>6.77</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/GRASIM.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/HAL.png</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd</t>
+          <t>Hindustan Aeronautics Ltd</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2415,51 +2407,51 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grasim Industries Limited is the flagship company of the Aditya Birla group, it ranks amongst India's largest private sector companies. On standalone basis, GIL's core businesses comprise of viscose Staple fibre (VSF), caustic soda, speciality chemicals, rayon-grade wood pulp (RGWP) with plants at multiple locations. It also has certain other businesses such as fertiliser, textile</t>
+          <t>Hindustan Aeronautics is engaged in the business of Manufacture of Aircraft and Helicopters and Repair, Maintenance of Aircraft and Helicopters</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.grasim.com/</t>
+          <t>https://hal-india.co.in/</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=GRASIM</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=HAL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/grasim-industries-ltd/GRASIM/500300/</t>
+          <t>https://www.bseindia.com/stock-share-price/hindustan-aeronautics-ltd/HAL/541154/</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J37" t="n">
-        <v>1411</v>
+        <v>465</v>
       </c>
       <c r="K37" t="n">
-        <v>9.300000000000001</v>
+        <v>38.9</v>
       </c>
       <c r="L37" t="n">
-        <v>6.9</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/HAL.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/HAVELLS.png</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hindustan Aeronautics Ltd</t>
+          <t>Havells India Ltd</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2469,51 +2461,52 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hindustan Aeronautics is engaged in the business of Manufacture of Aircraft and Helicopters and Repair, Maintenance of Aircraft and Helicopters</t>
+          <t>Havells India Limited is a leading Fast Moving Electrical Goods (FMEG) Company and a major power distribution equipment manufacturer with a strong global presence.
+It enjoys enviable market dominance across a wide spectrum of products, including Industrial &amp; Domestic Circuit Protection Devices, Cables &amp; Wires, Motors, Fans, Modular Switches, Home Appliances, Air Conditioners, Electric Water Heaters, Power Capacitors, Luminaires for Domestic, Commercial and Industrial</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://hal-india.co.in/</t>
+          <t>https://havells.com/</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=HAL</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=HAVELLS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/hindustan-aeronautics-ltd/HAL/541154/</t>
+          <t>https://www.bseindia.com/stock-share-price/havells-india-ltd/HAVELLS/517354/</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>465</v>
+        <v>124</v>
       </c>
       <c r="K38" t="n">
-        <v>38.9</v>
+        <v>24.4</v>
       </c>
       <c r="L38" t="n">
-        <v>28.9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/HAVELLS.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/HCLTECH.png</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Havells India Ltd</t>
+          <t>HCL Technologies Ltd</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2523,498 +2516,443 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Havells India Limited is a leading Fast Moving Electrical Goods (FMEG) Company and a major power distribution equipment manufacturer with a strong global presence.
-It enjoys enviable market dominance across a wide spectrum of products, including Industrial &amp; Domestic Circuit Protection Devices, Cables &amp; Wires, Motors, Fans, Modular Switches, Home Appliances, Air Conditioners, Electric Water Heaters, Power Capacitors, Luminaires for Domestic, Commercial and Industrial</t>
+          <t xml:space="preserve">HCL Tech is a leading global IT services company, which is ranked amongst the top five Indian IT services companies in terms of revenues. Since its inception into the global landscape after its IPO in 1999, HCL Tech has focused on transformational outsourcing, and offers an integrated portfolio of services including software-led IT solutions, remote infrastructure management, engineering and R&amp;D services and BPO. The company leverages its extensive global offshore infrastructure and network of offices in 46 </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://havells.com/</t>
+          <t>https://www.hcltech.com/</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=HAVELLS</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=HCLTECH</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/havells-india-ltd/HAVELLS/517354/</t>
+          <t>https://www.bseindia.com/stock-share-price/hcl-technologies-ltd/HCLTECH/532281/</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
-        <v>124</v>
+        <v>254</v>
       </c>
       <c r="K39" t="n">
-        <v>24.4</v>
+        <v>29.6</v>
       </c>
       <c r="L39" t="n">
-        <v>18</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/HCLTECH.png</t>
+          <t xml:space="preserve">https://mkt.in/static/mkt-icons/nifty100/HDFCBANK.png
+</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HCL Technologies Ltd</t>
+          <t>HDFC Bank Ltd</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AHDFCBANK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCL Tech is a leading global IT services company, which is ranked amongst the top five Indian IT services companies in terms of revenues. Since its inception into the global landscape after its IPO in 1999, HCL Tech has focused on transformational outsourcing, and offers an integrated portfolio of services including software-led IT solutions, remote infrastructure management, engineering and R&amp;D services and BPO. The company leverages its extensive global offshore infrastructure and network of offices in 46 </t>
+          <t>HDFC Bank Limited (also known as HDFC) is an Indian banking and financial services company headquartered in Mumbai. It is India's largest private sector bank by assets and the world's tenth-largest bank by market capitalization as of May 2024.
+As of April 2024, HDFC Bank has a market capitalization of $145 billion, making it the third-largest company on the Indian stock exchanges</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.hcltech.com/</t>
+          <t>http://www.hdfcbank.com/</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=HCLTECH</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=HDFCBANK</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/hcl-technologies-ltd/HCLTECH/532281/</t>
+          <t>https://www.bseindia.com/stock-share-price/hdfc-bank-ltd/HDFCBANK/500180/</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>254</v>
+        <v>601</v>
       </c>
       <c r="K40" t="n">
-        <v>29.6</v>
+        <v>7.67</v>
       </c>
       <c r="L40" t="n">
-        <v>23.3</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://mkt.in/static/mkt-icons/nifty100/HDFCBANK.png
-</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/HDFCLIFE.png</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HDFC Bank Ltd</t>
+          <t>HDFC Life Insurance Company Ltd</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AHDFCBANK</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AHDFCLIFE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HDFC Bank Limited (also known as HDFC) is an Indian banking and financial services company headquartered in Mumbai. It is India's largest private sector bank by assets and the world's tenth-largest bank by market capitalization as of May 2024.
-As of April 2024, HDFC Bank has a market capitalization of $145 billion, making it the third-largest company on the Indian stock exchanges</t>
+          <t>HDFC Life Insurance Company is engaged in carrying on the business of life insurance. The Company offers a range of individual and group insurance solutions.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>http://www.hdfcbank.com/</t>
+          <t>http://www.hdfclife.com/</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=HDFCBANK</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=HDFCLIFE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/hdfc-bank-ltd/HDFCBANK/500180/</t>
+          <t>https://www.bseindia.com/stock-share-price/hdfc-life-insurance-company-ltd/HDFCLIFE/540777/</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J41" t="n">
-        <v>601</v>
+        <v>73</v>
       </c>
       <c r="K41" t="n">
-        <v>7.67</v>
+        <v>6.61</v>
       </c>
       <c r="L41" t="n">
-        <v>17.1</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/HDFCLIFE.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/HEROMOTOCO.png</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd</t>
+          <t xml:space="preserve">Hero MotoCorp Ltd
+</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AHDFCLIFE</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AHEROMOTOCO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company is engaged in carrying on the business of life insurance. The Company offers a range of individual and group insurance solutions.</t>
+          <t>Hero Moto Corp earlier also known as \"Hero Honda\" is one of India's first motorcycle manufacturers.
+The company started in 1984 as a Technological collaboration with Honda, Japan. Before this collaboration, Hero was selling Cycles under the brand name, Hero Cycles.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>http://www.hdfclife.com/</t>
+          <t>http://www.heromotocorp.com/</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=HDFCLIFE</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=HEROMOTOCO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/hdfc-life-insurance-company-ltd/HDFCLIFE/540777/</t>
+          <t>https://www.bseindia.com/stock-share-price/hero-motocorp-ltd/HEROMOTOCO/500182/</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>73</v>
+        <v>951</v>
       </c>
       <c r="K42" t="n">
-        <v>6.61</v>
+        <v>29.1</v>
       </c>
       <c r="L42" t="n">
-        <v>11.4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/HEROMOTOCO.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/HINDALCO.png</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero MotoCorp Ltd
-</t>
+          <t>Hindalco Industries Ltd</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AHEROMOTOCO</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AHINDALCO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hero Moto Corp earlier also known as \"Hero Honda\" is one of India's first motorcycle manufacturers.
-The company started in 1984 as a Technological collaboration with Honda, Japan. Before this collaboration, Hero was selling Cycles under the brand name, Hero Cycles.</t>
+          <t>Incorporated in 1958, Hindalco Industries Ltd. is a flagship company of the Aditya Birla Group. The Co and its subsidiaries are primarily engaged in the production of Aluminium and Copper. It is also
+engaged in the manufacturing of aluminium sheet, extrusion and light gauge products for use in packaging markets like beverage and food, can and foil products, etc.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>http://www.heromotocorp.com/</t>
+          <t>http://www.hindalco.com/</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=HEROMOTOCO</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=HINDALCO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/hero-motocorp-ltd/HEROMOTOCO/500182/</t>
+          <t>https://www.bseindia.com/stock-share-price/hindalco-industries-ltd/HINDALCO/500440/</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>951</v>
+        <v>153</v>
       </c>
       <c r="K43" t="n">
-        <v>29.1</v>
+        <v>11.3</v>
       </c>
       <c r="L43" t="n">
-        <v>22</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/HINDALCO.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/HINDUNILVR.png</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hindalco Industries Ltd</t>
+          <t xml:space="preserve">Hindustan Unilever Ltd
+</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AHINDALCO</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AHINDUNILVR</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Incorporated in 1958, Hindalco Industries Ltd. is a flagship company of the Aditya Birla Group. The Co and its subsidiaries are primarily engaged in the production of Aluminium and Copper. It is also
-engaged in the manufacturing of aluminium sheet, extrusion and light gauge products for use in packaging markets like beverage and food, can and foil products, etc.</t>
+          <t>Hindustan Unilever is in the FMCG business comprising primarily of Home Care, Beauty &amp; Personal Care and Foods &amp; Refreshment segments. The Company has manufacturing facilities across the country and sells primarily in India.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>http://www.hindalco.com/</t>
+          <t>http://www.hul.co.in/</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=HINDALCO</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=HINDUNILVR</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/hindalco-industries-ltd/HINDALCO/500440/</t>
+          <t>https://www.bseindia.com/stock-share-price/hindustan-unilever-ltd/HINDUNILVR/500696/</t>
         </is>
       </c>
       <c r="I44" t="n">
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="K44" t="n">
-        <v>11.3</v>
+        <v>27.2</v>
       </c>
       <c r="L44" t="n">
-        <v>10.2</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/HINDUNILVR.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/ICICIBANK.png</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hindustan Unilever Ltd
-</t>
+          <t>ICICI Bank Ltd</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AHINDUNILVR</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AICICIBANK</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hindustan Unilever is in the FMCG business comprising primarily of Home Care, Beauty &amp; Personal Care and Foods &amp; Refreshment segments. The Company has manufacturing facilities across the country and sells primarily in India.</t>
+          <t>ICICI Bank is the second-largest private sector bank in India offering a diversified portfolio of financial products and services to retail, SME and corporate customers. The Bank has an extensive network of branches, ATMs and other touch-points</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>http://www.hul.co.in/</t>
+          <t>http://www.icicibank.com/</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=HINDUNILVR</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=ICICIBANK</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/hindustan-unilever-ltd/HINDUNILVR/500696/</t>
+          <t>https://www.bseindia.com/stock-share-price/icici-bank-ltd/ICICIBANK/532174/</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>216</v>
+        <v>365</v>
       </c>
       <c r="K45" t="n">
-        <v>27.2</v>
+        <v>7.6</v>
       </c>
       <c r="L45" t="n">
-        <v>20.2</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/ICICIBANK.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/ICICIGI.png</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ICICI Bank Ltd</t>
+          <t>ICICI Lombard General Insurance Company Ltd</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AICICIBANK</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AICICIGI</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ICICI Bank is the second-largest private sector bank in India offering a diversified portfolio of financial products and services to retail, SME and corporate customers. The Bank has an extensive network of branches, ATMs and other touch-points</t>
+          <t>ICICI Lombard General Insurance Co. Ltd is one of the leading and established private sector general insurance companies in India. It offers a well-diversified range of products and risk management solutions through multiple distribution channels</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>http://www.icicibank.com/</t>
+          <t>http://www.icicilombard.com/</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=ICICIBANK</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=ICICIGI</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/icici-bank-ltd/ICICIBANK/532174/</t>
+          <t>https://www.bseindia.com/stock-share-price/icici-lombard-general-insurance-company-ltd/ICICIGI/540716/</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>365</v>
+        <v>275</v>
       </c>
       <c r="K46" t="n">
-        <v>7.6</v>
+        <v>22.5</v>
       </c>
       <c r="L46" t="n">
-        <v>18.8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/ICICIGI.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/ICICIPRULI.png</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ICICI Lombard General Insurance Company Ltd</t>
+          <t>ICICI Prudential Life Insurance Company Ltd</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AICICIGI</t>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
-        <is>
-          <t>ICICI Lombard General Insurance Co. Ltd is one of the leading and established private sector general insurance companies in India. It offers a well-diversified range of products and risk management solutions through multiple distribution channels</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>http://www.icicilombard.com/</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=ICICIGI</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>https://www.bseindia.com/stock-share-price/icici-lombard-general-insurance-company-ltd/ICICIGI/540716/</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>10</v>
-      </c>
-      <c r="J47" t="n">
-        <v>275</v>
-      </c>
-      <c r="K47" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="L47" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/ICICIPRULI.png</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>ICICI Prudential Life Insurance Company Ltd</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
         <is>
           <t xml:space="preserve">ICICI Prudential Life Insurance Company Ltd carries on business of providing life insurance, pensions and health insurance products to individuals and groups. The business is conducted in participating, non-participating and unit linked lines of business. These products are distributed through individual agents, corporate agents, banks, brokers, sales force and company's website.[1]
 It is promoted by ICICI Bank and Prudential Corporation :-
@@ -3023,1520 +2961,1520 @@
 </t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.iciciprulife.com/</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.bseindia.com/stock-share-price/icici-prudential-life-insurance-company-ltd/ICICIPRULI/540133/</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>10</v>
+      </c>
+      <c r="J47" t="n">
+        <v>80</v>
+      </c>
+      <c r="K47" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="L47" t="n">
+        <v>8.07</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://rb.gy/rv6gr8
+</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Interglobe Aviation Ltd</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AINDIGO</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Interglobe Aviation Ltd (Indigo) is India's largest passenger airline operating as a low-cost carrier. Serving 86 destinations including 24 international destinations, it provides passengers with a simple, unbundled product, fulfilling its singular brand promise of providing \"low fares, on-time flights, and a courteous and hassle-free service\" to its customers. IndiGo commenced operations in August 2006 with a single aircraft and has grown its fleet to 262 aircrafts.</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.iciciprulife.com/</t>
+          <t>http://www.goindigo.in/</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=ICICIPRULI</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=INDIGO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/icici-prudential-life-insurance-company-ltd/ICICIPRULI/540133/</t>
+          <t>https://www.bseindia.com/stock-share-price/interglobe-aviation-ltd/INDIGO/539448/</t>
         </is>
       </c>
       <c r="I48" t="n">
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="K48" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L48" t="n">
-        <v>8.07</v>
-      </c>
+        <v>24.5</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://rb.gy/rv6gr8
-</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/INDUSINDBK.png</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Interglobe Aviation Ltd</t>
+          <t>IndusInd Bank Ltd</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AINDIGO</t>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Interglobe Aviation Ltd (Indigo) is India's largest passenger airline operating as a low-cost carrier. Serving 86 destinations including 24 international destinations, it provides passengers with a simple, unbundled product, fulfilling its singular brand promise of providing \"low fares, on-time flights, and a courteous and hassle-free service\" to its customers. IndiGo commenced operations in August 2006 with a single aircraft and has grown its fleet to 262 aircrafts.</t>
+          <t>IndusInd Bank Limited was incorporated in 1994 as a commercial bank under the Banking Regulation Act, 1949. The Bank is publicly held</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>http://www.goindigo.in/</t>
+          <t>https://www.indusind.com/in/en/personal.html</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=INDIGO</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=INDUSINDBK</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/interglobe-aviation-ltd/INDIGO/539448/</t>
+          <t>https://www.bseindia.com/stock-share-price/indusind-bank-ltd/INDUSINDBK/532187/</t>
         </is>
       </c>
       <c r="I49" t="n">
         <v>10</v>
       </c>
       <c r="J49" t="n">
-        <v>97</v>
+        <v>807</v>
       </c>
       <c r="K49" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="L49" t="inlineStr"/>
+        <v>7.93</v>
+      </c>
+      <c r="L49" t="n">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/INDUSINDBK.png</t>
+          <t>https://images.5paisa.com/MarketIcons/INFY.png</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IndusInd Bank Ltd</t>
+          <t>Infosys Ltd</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AINFY</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IndusInd Bank Limited was incorporated in 1994 as a commercial bank under the Banking Regulation Act, 1949. The Bank is publicly held</t>
+          <t>Infosys Ltd provides consulting, technology, outsourcing and next-generation digital services to enable clients to execute strategies for their digital transformation</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.indusind.com/in/en/personal.html</t>
+          <t>http://www.infosys.com/</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=INDUSINDBK</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=INFY</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/indusind-bank-ltd/INDUSINDBK/532187/</t>
+          <t>https://www.bseindia.com/stock-share-price/infosys-ltd/INFY/500209/</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
-        <v>807</v>
+        <v>218</v>
       </c>
       <c r="K50" t="n">
-        <v>7.93</v>
+        <v>40</v>
       </c>
       <c r="L50" t="n">
-        <v>15.2</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://images.5paisa.com/MarketIcons/INFY.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/IOC.png</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Infosys Ltd</t>
+          <t xml:space="preserve">Indian Oil Corporation
+</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AINFY</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AIOC</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Infosys Ltd provides consulting, technology, outsourcing and next-generation digital services to enable clients to execute strategies for their digital transformation</t>
+          <t>Indian Oil Corporation Limited, trading as IndianOil, is an Indian multinational oil and gas company under the ownership of Government of India and administrative control of the Ministry of Petroleum and Natural Gas.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>http://www.infosys.com/</t>
+          <t>https://www.iocl.com/</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=INFY</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=IOC</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/infosys-ltd/INFY/500209/</t>
+          <t>https://www.bseindia.com/stock-share-price/indian-oil-corporation-ltd/ioc/530965/</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>218</v>
+        <v>129</v>
       </c>
       <c r="K51" t="n">
-        <v>40</v>
+        <v>21.31</v>
       </c>
       <c r="L51" t="n">
-        <v>31.8</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/IOC.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/IRCTC.png</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indian Oil Corporation
-</t>
+          <t>Indian Railway Catering &amp; Tourism Corporation Ltd</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AIOC</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AIRCTC</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Indian Oil Corporation Limited, trading as IndianOil, is an Indian multinational oil and gas company under the ownership of Government of India and administrative control of the Ministry of Petroleum and Natural Gas.</t>
+          <t>Incorporated in 1999, IRCTC is a Mini Ratna (Category 1, Central Public Sector Enterprises ) and the only company authorized by the Indian government to provide online railway tickets, catering services, and packaged drinking water
+at railway stations and trains in India</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.iocl.com/</t>
+          <t>http://www.irctc.com/</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=IOC</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=IRCTC</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/indian-oil-corporation-ltd/ioc/530965/</t>
+          <t>https://www.bseindia.com/stock-share-price/indian-railway-catering-tourism-corporation-ltd/IRCTC/542830/</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
-        <v>129</v>
+        <v>44</v>
       </c>
       <c r="K52" t="n">
-        <v>21.31</v>
+        <v>53.8</v>
       </c>
       <c r="L52" t="n">
-        <v>25.44</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/IRCTC.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/IRFC.png</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Indian Railway Catering &amp; Tourism Corporation Ltd</t>
+          <t>Indian Railway Finance Corporation Ltd</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AIRCTC</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AIRFC</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Incorporated in 1999, IRCTC is a Mini Ratna (Category 1, Central Public Sector Enterprises ) and the only company authorized by the Indian government to provide online railway tickets, catering services, and packaged drinking water
-at railway stations and trains in India</t>
+          <t>Incorporated in 1986, Indian Railway Finance Corporation borrows funds from the financial markets to finance the acquisition / creation of assets which are then leased out to the Indian Railways as finance lease</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>http://www.irctc.com/</t>
+          <t>https://irfc.co.in/</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=IRCTC</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=IRFC</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/indian-railway-catering-tourism-corporation-ltd/IRCTC/542830/</t>
+          <t>https://www.bseindia.com/stock-share-price/indian-railway-finance-corporation-ltd/IRFC/543257/</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="K53" t="n">
-        <v>53.8</v>
+        <v>5.73</v>
       </c>
       <c r="L53" t="n">
-        <v>40.4</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/IRFC.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/ITC.png</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indian Railway Finance Corporation Ltd</t>
+          <t xml:space="preserve">ITC Ltd
+</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AIRFC</t>
+          <t>https://in.tradingview.com/chart/?symbol=ITC</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Incorporated in 1986, Indian Railway Finance Corporation borrows funds from the financial markets to finance the acquisition / creation of assets which are then leased out to the Indian Railways as finance lease</t>
+          <t>ITC Limited is an Indian conglomerate, headquartered in Kolkata. It has a presence across six business segments, namely FMCG, hotels, agribusiness, information technology, paper products, and packaging.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://irfc.co.in/</t>
+          <t>https://www.itcportal.com/</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=IRFC</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=ITC</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/indian-railway-finance-corporation-ltd/IRFC/543257/</t>
+          <t>https://www.bseindia.com/stock-share-price/itc-ltd/itc/500875/</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="K54" t="n">
-        <v>5.73</v>
+        <v>34.76</v>
       </c>
       <c r="L54" t="n">
-        <v>13.7</v>
+        <v>29.47</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/ITC.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/JINDALSTEL.png</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITC Ltd
-</t>
+          <t>Jindal Steel &amp; Power Ltd</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=ITC</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AJINDALSTEL</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ITC Limited is an Indian conglomerate, headquartered in Kolkata. It has a presence across six business segments, namely FMCG, hotels, agribusiness, information technology, paper products, and packaging.</t>
+          <t>Jindal Steel &amp; Power Ltd is one of the India's leading steel producers with significant presence in sectors like mining and power generation. The group has global presence through subsidiaries, mainly in Australia, Botswana, Indonesia, Mauritius, Mozambique, Madagascar, Namibia, South Africa, Tanzania and Zambia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.itcportal.com/</t>
+          <t>http://www.jindalsteelpower.com/</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=ITC</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=JINDALSTEL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/itc-ltd/itc/500875/</t>
+          <t>https://www.bseindia.com/stock-share-price/jindal-steel-power-ltd/JINDALSTEL/532286/</t>
         </is>
       </c>
       <c r="I55" t="n">
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>60</v>
+        <v>464</v>
       </c>
       <c r="K55" t="n">
-        <v>34.76</v>
+        <v>13.2</v>
       </c>
       <c r="L55" t="n">
-        <v>29.47</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/JINDALSTEL.png</t>
+          <t xml:space="preserve">https://mkt.in/static/mkt-icons/nifty100/JIOFIN.png
+</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jindal Steel &amp; Power Ltd</t>
+          <t>Jio Financial Services Ltd</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AJINDALSTEL</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AJIOFIN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jindal Steel &amp; Power Ltd is one of the India's leading steel producers with significant presence in sectors like mining and power generation. The group has global presence through subsidiaries, mainly in Australia, Botswana, Indonesia, Mauritius, Mozambique, Madagascar, Namibia, South Africa, Tanzania and Zambia</t>
+          <t>Jio Financial Services Ltd is an Indian financial services company, based in Mumbai. Originally a subsidiary of Reliance Industries, it was demerged as an independent entity and listed on the Indian stock exchanges in August 2023.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>http://www.jindalsteelpower.com/</t>
+          <t>https://www.jfs.in/</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=JINDALSTEL</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=JIOFIN</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/jindal-steel-power-ltd/JINDALSTEL/532286/</t>
+          <t>https://bseindia.com/stock-share-price/jio-financial-services-ltd/jiofin/543940/</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>464</v>
+        <v>216</v>
       </c>
       <c r="K56" t="n">
-        <v>13.2</v>
+        <v>2.16</v>
       </c>
       <c r="L56" t="n">
-        <v>14.1</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://mkt.in/static/mkt-icons/nifty100/JIOFIN.png
-</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/JSWENERGY.png</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jio Financial Services Ltd</t>
+          <t>JSW Energy Ltd</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AJIOFIN</t>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
-        <is>
-          <t>Jio Financial Services Ltd is an Indian financial services company, based in Mumbai. Originally a subsidiary of Reliance Industries, it was demerged as an independent entity and listed on the Indian stock exchanges in August 2023.</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>https://www.jfs.in/</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=JIOFIN</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>https://bseindia.com/stock-share-price/jio-financial-services-ltd/jiofin/543940/</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>10</v>
-      </c>
-      <c r="J57" t="n">
-        <v>216</v>
-      </c>
-      <c r="K57" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>JSWENERGY</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/JSWENERGY.png</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>JSW Energy Ltd</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
         <is>
           <t xml:space="preserve">JSW Energy Ltd and its subsidiaries are primarily engaged in the business of generation of power from its power assets located at Karnataka, Maharashtra, Nandyal and Salboni. It is the holding company for the JSW group's power business.
 The company also has a JV company engaged in mining activities and an associate engaged in manufacturing of turbines.[1]
 </t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://www.jsw.in/</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=JSWENERGY</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.bseindia.com/stock-share-price/jsw-energy-ltd/JSWENERGY/533148/</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>10</v>
+      </c>
+      <c r="J57" t="n">
+        <v>160</v>
+      </c>
+      <c r="K57" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="L57" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://mkt.in/static/mkt-icons/nifty100/JSWSTEEL.png</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>JSW Steel Ltd</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AJSWSTEEL</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>JSW Steel Limited is an Indian multinational steel producer based in Mumbai and is a flagship company of the JSW Group.</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.jsw.in/</t>
+          <t>https://www.jswsteel.in/</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=JSWENERGY</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=JSWSTEEL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/jsw-energy-ltd/JSWENERGY/533148/</t>
+          <t>https://www.bseindia.com/stock-share-price/jsw-steel-ltd/jswsteel/500228/</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>160</v>
+        <v>326</v>
       </c>
       <c r="K58" t="n">
-        <v>8.59</v>
+        <v>13.36</v>
       </c>
       <c r="L58" t="n">
-        <v>8.4</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/JSWSTEEL.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/KOTAKBANK.png</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>JSW Steel Ltd</t>
+          <t xml:space="preserve">Kotak Mahindra Bank Ltd
+</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AJSWSTEEL</t>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>JSW Steel Limited is an Indian multinational steel producer based in Mumbai and is a flagship company of the JSW Group.</t>
+          <t xml:space="preserve">Kotak Mahindra Bank is a diversified financial services group providing a wide range of banking and financial services including Retail Banking, Treasury and Corporate Banking, Investment Banking, Stock Broking, Vehicle Finance, Advisory services, Asset Management, Life Insurance and General Insurance.[1]
+</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.jswsteel.in/</t>
+          <t>https://www.kotak.com/en/home.html</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=JSWSTEEL</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=KOTAKBANK</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/jsw-steel-ltd/jswsteel/500228/</t>
+          <t>https://www.bseindia.com/stock-share-price/kotak-mahindra-bank-ltd/KOTAKBANK/500247/</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
-        <v>326</v>
+        <v>654</v>
       </c>
       <c r="K59" t="n">
-        <v>13.36</v>
+        <v>7.86</v>
       </c>
       <c r="L59" t="n">
-        <v>11.66</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/KOTAKBANK.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/LICI.png</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kotak Mahindra Bank Ltd
-</t>
+          <t>Life Insurance Corporation of India</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3ALICI</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kotak Mahindra Bank is a diversified financial services group providing a wide range of banking and financial services including Retail Banking, Treasury and Corporate Banking, Investment Banking, Stock Broking, Vehicle Finance, Advisory services, Asset Management, Life Insurance and General Insurance.[1]
-</t>
+          <t>Life Insurance Corporation of India is an Indian multinational public sector life insurance company headquartered in Mumbai</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.kotak.com/en/home.html</t>
+          <t>https://www.licindia.in/</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=KOTAKBANK</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=LICI</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/kotak-mahindra-bank-ltd/KOTAKBANK/500247/</t>
+          <t>https://www.bseindia.com/stock-share-price/life-insurance-corporation-of-india/lici/543526/</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>654</v>
+        <v>154</v>
       </c>
       <c r="K60" t="n">
-        <v>7.86</v>
+        <v>63.79</v>
       </c>
       <c r="L60" t="n">
-        <v>15.1</v>
+        <v>63.61</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/LICI.png</t>
+          <t>https://rb.gy/b35o6u</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Life Insurance Corporation of India</t>
+          <t>Macrotech Developers Ltd</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3ALICI</t>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Life Insurance Corporation of India is an Indian multinational public sector life insurance company headquartered in Mumbai</t>
+          <t xml:space="preserve">Macrotech Developers Ltd is primarily engaged in the business of real estate development. It is among the largest real estate developers in terms of presales and development pipeline in India with a presence in MMR, Pune and entered in Bengaluru market in Nov'23.[1]
+</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.licindia.in/</t>
+          <t>https://www.lodhagroup.com/</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=LICI</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=LODHA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/life-insurance-corporation-of-india/lici/543526/</t>
+          <t>https://www.bseindia.com/stock-share-price/macrotech-developers-ltd/LODHA/543287/</t>
         </is>
       </c>
       <c r="I61" t="n">
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="K61" t="n">
-        <v>63.79</v>
+        <v>11.1</v>
       </c>
       <c r="L61" t="n">
-        <v>63.61</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://rb.gy/b35o6u</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/LT.png</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Macrotech Developers Ltd</t>
+          <t>Larsen &amp; Toubro Ltd</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3ALT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Macrotech Developers Ltd is primarily engaged in the business of real estate development. It is among the largest real estate developers in terms of presales and development pipeline in India with a presence in MMR, Pune and entered in Bengaluru market in Nov'23.[1]
-</t>
+          <t xml:space="preserve">Lithuania, officially the Republic of Lithuania, is a country in the Baltic region of Europe. It is one of three Baltic states and lies on the eastern shore of the Baltic Sea, bordered by Latvia to the north, Belarus to the east and south, Poland to the south, and the Russian semi-exclave of Kaliningrad Oblast to the southwest, with a maritime border with Sweden to the west. </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.lodhagroup.com/</t>
+          <t>https://www.larsentoubro.com/</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=LODHA</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=LT</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/macrotech-developers-ltd/LODHA/543287/</t>
+          <t>https://www.bseindia.com/stock-share-price/larsen--toubro-ltd/lt/500510/</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
-        <v>183</v>
+        <v>635</v>
       </c>
       <c r="K62" t="n">
-        <v>11.1</v>
+        <v>17.18</v>
       </c>
       <c r="L62" t="n">
-        <v>10.7</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/LT.png</t>
-        </is>
-      </c>
+          <t>LTIM</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Ltd</t>
+          <t>LTIMindtree Ltd</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3ALT</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/ABB.png</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lithuania, officially the Republic of Lithuania, is a country in the Baltic region of Europe. It is one of three Baltic states and lies on the eastern shore of the Baltic Sea, bordered by Latvia to the north, Belarus to the east and south, Poland to the south, and the Russian semi-exclave of Kaliningrad Oblast to the southwest, with a maritime border with Sweden to the west. </t>
+          <t>LTIMindtree Limited is an Indian multinational information technology services and consulting company based in Mumbai. A subsidiary of Larsen &amp; Toubro, the company was incorporated in 1996 and employs more than 81,000 people</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.larsentoubro.com/</t>
+          <t>https://www.ltimindtree.com/</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=LT</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=LTIM</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/larsen--toubro-ltd/lt/500510/</t>
+          <t>https://www.bseindia.com/stock-share-price/ltimindtree-ltd/ltim/540005/</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>635</v>
+        <v>711</v>
       </c>
       <c r="K63" t="n">
-        <v>17.18</v>
+        <v>34.1</v>
       </c>
       <c r="L63" t="n">
-        <v>10.49</v>
+        <v>26.04</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LTIM</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://mkt.in/static/mkt-icons/nifty100/M&amp;M.png</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LTIMindtree Ltd</t>
+          <t xml:space="preserve">Mahindra &amp; Mahindra Ltd
+</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/ABB.png</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AM&amp;M=</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>LTIMindtree Limited is an Indian multinational information technology services and consulting company based in Mumbai. A subsidiary of Larsen &amp; Toubro, the company was incorporated in 1996 and employs more than 81,000 people</t>
+          <t>Mahindra &amp; Mahindra is an Indian automobile manufacturing company headquartered in Mumbai, Maharashtra. It was established in 1945 as Mahindra &amp; Mohammed and later renamed Mahindra &amp; Mahindra.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.ltimindtree.com/</t>
+          <t>https://auto.mahindra.com/</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=LTIM</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=M&amp;M</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/ltimindtree-ltd/ltim/540005/</t>
+          <t>https://www.bseindia.com/stock-share-price/mahindra--mahindra-ltd/mm/500520/</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
-        <v>711</v>
+        <v>567</v>
       </c>
       <c r="K64" t="n">
-        <v>34.1</v>
+        <v>26.98</v>
       </c>
       <c r="L64" t="n">
-        <v>26.04</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/M&amp;M.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/MARUTI.png</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mahindra &amp; Mahindra Ltd
-</t>
+          <t>Maruti Suzuki India Ltd</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AM&amp;M=</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AMARUTI</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra is an Indian automobile manufacturing company headquartered in Mumbai, Maharashtra. It was established in 1945 as Mahindra &amp; Mohammed and later renamed Mahindra &amp; Mahindra.</t>
+          <t>Maruti Suzuki India Limited is a publicly listed Indian subsidiary of Japanese automaker Suzuki Motor Corporation. It is the largest automobile manufacturer in India, specialising in small cars.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://auto.mahindra.com/</t>
+          <t>https://www.marutisuzuki.com/</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=M&amp;M</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=MARUTI</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/mahindra--mahindra-ltd/mm/500520/</t>
+          <t>https://www.bseindia.com/stock-share-price/maruti-suzuki-india-ltd/maruti/532500/</t>
         </is>
       </c>
       <c r="I65" t="n">
         <v>5</v>
       </c>
       <c r="J65" t="n">
-        <v>567</v>
+        <v>2835</v>
       </c>
       <c r="K65" t="n">
-        <v>26.98</v>
+        <v>23.67</v>
       </c>
       <c r="L65" t="n">
-        <v>17.99</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/MARUTI.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/MOTHERSON.png</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Ltd</t>
+          <t>Samvardhana Motherson International Ltd</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AMARUTI</t>
+          <t>https://in.tradingview.com/chart/?symbol=BSE%3AMOTHERSON</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Limited is a publicly listed Indian subsidiary of Japanese automaker Suzuki Motor Corporation. It is the largest automobile manufacturer in India, specialising in small cars.</t>
+          <t>Motherson Sumi Systems is engaged primarily in the manufacturer and sale of components to automotive original equipment manufacturers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.marutisuzuki.com/</t>
+          <t>http://www.motherson.com/</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=MARUTI</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=MOTHERSON</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/maruti-suzuki-india-ltd/maruti/532500/</t>
+          <t>https://www.bseindia.com/stock-share-price/samvardhana-motherson-international-ltd/MOTHERSON/517334/</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>2835</v>
+        <v>46</v>
       </c>
       <c r="K66" t="n">
-        <v>23.67</v>
+        <v>13.7</v>
       </c>
       <c r="L66" t="n">
-        <v>15.75</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/MOTHERSON.png</t>
+          <t>https://assets-netstorage.groww.in/stock-assets/logos2/InfoEdgIndia_32670259917_18844.png</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Samvardhana Motherson International Ltd</t>
+          <t>Info Edge (India) Ltd</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=BSE%3AMOTHERSON</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3ANAUKRI</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Motherson Sumi Systems is engaged primarily in the manufacturer and sale of components to automotive original equipment manufacturers</t>
+          <t>Info Edge is India's premier online classified company with a portfolio of brands. It owns various brands in different fields like naukri.com (online recruitment), 99acres.com (online real estate), jeevansathi.com (online matrimonial) as well as shiksha.com (online education information services). It also acts as an investor and has invested in many start-ups in the online space and is actively growing its investment portfolio.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>http://www.motherson.com/</t>
+          <t>http://www.infoedge.in/</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=MOTHERSON</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=NAUKRI</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/samvardhana-motherson-international-ltd/MOTHERSON/517334/</t>
+          <t>https://www.bseindia.com/stock-share-price/info-edge-india-ltd/NAUKRI/532777/</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>46</v>
+        <v>3225</v>
       </c>
       <c r="K67" t="n">
-        <v>13.7</v>
+        <v>3.65</v>
       </c>
       <c r="L67" t="n">
-        <v>11.8</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://assets-netstorage.groww.in/stock-assets/logos2/InfoEdgIndia_32670259917_18844.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/NESTLEIND.png</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Info Edge (India) Ltd</t>
+          <t>Nestle India Ltd</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3ANAUKRI</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3ANESTLEIND</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Info Edge is India's premier online classified company with a portfolio of brands. It owns various brands in different fields like naukri.com (online recruitment), 99acres.com (online real estate), jeevansathi.com (online matrimonial) as well as shiksha.com (online education information services). It also acts as an investor and has invested in many start-ups in the online space and is actively growing its investment portfolio.</t>
+          <t>Nestle India Limited is the Indian subsidiary of Nestle which is a Swiss multinational company. The company is headquartered in Gurgaon, Haryana. The company's products include food, beverages, chocolate, and confectioneries.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>http://www.infoedge.in/</t>
+          <t>https://www.nestle.in/</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=NAUKRI</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=NESTLEIND</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/info-edge-india-ltd/NAUKRI/532777/</t>
+          <t>https://www.bseindia.com/stock-share-price/nestle-india-ltd/nestleind/500790/</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>3225</v>
+        <v>41</v>
       </c>
       <c r="K68" t="n">
-        <v>3.65</v>
+        <v>185.43</v>
       </c>
       <c r="L68" t="n">
-        <v>2.44</v>
+        <v>135.61</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/NESTLEIND.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/HEROMOTOCO.png</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nestle India Ltd</t>
+          <t xml:space="preserve">NHPC Ltd
+</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3ANESTLEIND</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3ANHPC</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nestle India Limited is the Indian subsidiary of Nestle which is a Swiss multinational company. The company is headquartered in Gurgaon, Haryana. The company's products include food, beverages, chocolate, and confectioneries.</t>
+          <t>NHPC, a Mini Ratna category I public sector utility, is Government of India's flagship hydroelectric generation company. The company is primarily involved in the generation and sale of bulk power to various Power Utilities. Its other business includes providing project management / construction contracts/ consultancy assignment services and trading of power.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.nestle.in/</t>
+          <t>http://www.nhpcindia.com/</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=NESTLEIND</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=NHPC</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/nestle-india-ltd/nestleind/500790/</t>
+          <t>https://www.bseindia.com/stock-share-price/nhpc-ltd/NHPC/533098/</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J69" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K69" t="n">
-        <v>185.43</v>
+        <v>7.67</v>
       </c>
       <c r="L69" t="n">
-        <v>135.61</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/HEROMOTOCO.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/NTPC.png</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">NHPC Ltd
-</t>
+          <t>NTPC Ltd</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3ANHPC</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3ANTPC</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>NHPC, a Mini Ratna category I public sector utility, is Government of India's flagship hydroelectric generation company. The company is primarily involved in the generation and sale of bulk power to various Power Utilities. Its other business includes providing project management / construction contracts/ consultancy assignment services and trading of power.</t>
+          <t>NTPC Limited, formerly known as National Thermal Power Corporation, is an Indian central Public Sector Undertaking under the ownership of the Ministry of Power and the Government of India, who is engaged in the generation of electricity and other activities.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>http://www.nhpcindia.com/</t>
+          <t>https://ntpc.co.in/</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=NHPC</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=NTPC</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/nhpc-ltd/NHPC/533098/</t>
+          <t>https://www.bseindia.com/stock-share-price/ntpc-ltd/ntpc/532555/</t>
         </is>
       </c>
       <c r="I70" t="n">
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>40</v>
+        <v>174</v>
       </c>
       <c r="K70" t="n">
-        <v>7.67</v>
+        <v>10.58</v>
       </c>
       <c r="L70" t="n">
-        <v>9.609999999999999</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/NTPC.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/ONGC.png</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NTPC Ltd</t>
+          <t>Oil &amp; Natural Gas Corpn Ltd</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3ANTPC</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3AONGC</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>NTPC Limited, formerly known as National Thermal Power Corporation, is an Indian central Public Sector Undertaking under the ownership of the Ministry of Power and the Government of India, who is engaged in the generation of electricity and other activities.</t>
+          <t xml:space="preserve">The Oil and Natural Gas Corporation is an Indian government-owned-oil and gas explorer and producer. It is under the ownership of Ministry of Petroleum and Natural Gas, Government of India. Its registered office is in New Delhi. </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://ntpc.co.in/</t>
+          <t>https://www.ongcindia.com/</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=NTPC</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=ONGC</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/ntpc-ltd/ntpc/532555/</t>
+          <t>https://www.bseindia.com/stock-share-price/oil-and-natural-gas-corporation-ltd/ongc/500312/</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J71" t="n">
-        <v>174</v>
+        <v>275</v>
       </c>
       <c r="K71" t="n">
-        <v>10.58</v>
+        <v>19.71</v>
       </c>
       <c r="L71" t="n">
-        <v>12.52</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/ONGC.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/PFC.png</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oil &amp; Natural Gas Corpn Ltd</t>
+          <t>Power Finance Corporation Ltd</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3AONGC</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3APFC</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Oil and Natural Gas Corporation is an Indian government-owned-oil and gas explorer and producer. It is under the ownership of Ministry of Petroleum and Natural Gas, Government of India. Its registered office is in New Delhi. </t>
+          <t>Power Finance Corporation Ltd. is an Indian public sector company engaged in infrastructure finance activities.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.ongcindia.com/</t>
+          <t>https://www.pfcindia.com/</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=ONGC</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=PFC</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/oil-and-natural-gas-corporation-ltd/ongc/500312/</t>
+          <t>https://www.bseindia.com/stock-share-price/power-finance-corporation-ltd/pfc/532810/</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="K72" t="n">
-        <v>19.71</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>14.32</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/PFC.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/PIDILITIND.png</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Ltd</t>
+          <t>Pidilite Industries Ltd</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3APFC</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3APIDILITIND</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Ltd. is an Indian public sector company engaged in infrastructure finance activities.</t>
+          <t>Pidilite Industries Limited is a leading manufacturer of adhesives and sealants, construction chemicals, craftsmen products, DIY products and polymer emulsions in India. Most of the products have been developed through strong in-house R&amp;D. Our brand name Fevicol has become synonymous with adhesives to millions in India and is ranked amongst the most trusted brands in the country</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.pfcindia.com/</t>
+          <t>http://www.pidilite.com/</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=PFC</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=PIDILITIND</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/power-finance-corporation-ltd/pfc/532810/</t>
+          <t>https://www.bseindia.com/stock-share-price/pidilite-industries-ltd/PIDILITIND/500331/</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>333</v>
+        <v>171</v>
       </c>
       <c r="K73" t="n">
-        <v>9.960000000000001</v>
+        <v>29.7</v>
       </c>
       <c r="L73" t="n">
-        <v>19.49</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/PIDILITIND.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/PNB.png</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pidilite Industries Ltd</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3APIDILITIND</t>
+          <t>https://in.tradingview.com/chart/?symbol=NSE%3APNB</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Pidilite Industries Limited is a leading manufacturer of adhesives and sealants, construction chemicals, craftsmen products, DIY products and polymer emulsions in India. Most of the products have been developed through strong in-house R&amp;D. Our brand name Fevicol has become synonymous with adhesives to millions in India and is ranked amongst the most trusted brands in the country</t>
+          <t xml:space="preserve">Punjab National Bank is an Indian government bank based in New Delhi. It was founded in May 1894 and is the second-largest public sector bank in India in terms of its business volumes, with over 180 million customers, 12,248 branches, and 13,000+ ATMs. </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>http://www.pidilite.com/</t>
+          <t>https://www.pnbindia.in/</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=PIDILITIND</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=PNB</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/pidilite-industries-ltd/PIDILITIND/500331/</t>
+          <t>https://www.bseindia.com/stock-share-price/punjab-national-bank/pnb/532461/</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
-        <v>171</v>
+        <v>110</v>
       </c>
       <c r="K74" t="n">
-        <v>29.7</v>
+        <v>1.63</v>
       </c>
       <c r="L74" t="n">
-        <v>22.8</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/PNB.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/POWERGRID.png</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>Power Grid Corporation of India Ltd</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/?symbol=NSE%3APNB</t>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Punjab National Bank is an Indian government bank based in New Delhi. It was founded in May 1894 and is the second-largest public sector bank in India in terms of its business volumes, with over 180 million customers, 12,248 branches, and 13,000+ ATMs. </t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>https://www.pnbindia.in/</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=PNB</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>https://www.bseindia.com/stock-share-price/punjab-national-bank/pnb/532461/</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>2</v>
-      </c>
-      <c r="J75" t="n">
-        <v>110</v>
-      </c>
-      <c r="K75" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="L75" t="n">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>POWERGRID</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/POWERGRID.png</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Power Grid Corporation of India Ltd</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
         <is>
           <t xml:space="preserve">Power Grid Corporation of India Limited is a Maharatna CPSU and India's largest electric power transmission company. GoI holds a 51.34% stake in the company as on March 31, 2021. PGCIL was incorporated in 1989 to set up extra-high voltage alternating current and high-voltage direct current (HVDC) transmission lines.
 The company moves large blocks of power from the central generating agencies and areas that have surplus power to load centres within and across regions. It is under the administrative control of the Ministry of Power, GoI.
@@ -4544,48 +4482,103 @@
 </t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://www.powergrid.in/</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=POWERGRID</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.bseindia.com/stock-share-price/power-grid-corporation-of-india-ltd/POWERGRID/532898/</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>10</v>
+      </c>
+      <c r="J75" t="n">
+        <v>99</v>
+      </c>
+      <c r="K75" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://mkt.in/static/mkt-icons/nifty100/RECLTD.png</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>REC Ltd</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>REC is a Central Public Sector Undertaking under the Ministry of Power involved in financing projects in the complete power sector value chain from generation to distribution. [1]</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.powergrid.in/</t>
+          <t>https://recindia.nic.in/</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=POWERGRID</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=RECLTD</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/power-grid-corporation-of-india-ltd/POWERGRID/532898/</t>
+          <t>https://www.bseindia.com/stock-share-price/rec-ltd/RECLTD/532955/</t>
         </is>
       </c>
       <c r="I76" t="n">
         <v>10</v>
       </c>
       <c r="J76" t="n">
-        <v>99</v>
+        <v>279</v>
       </c>
       <c r="K76" t="n">
-        <v>13.2</v>
+        <v>10</v>
       </c>
       <c r="L76" t="n">
-        <v>19</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/RECLTD.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/RELIANCE.png</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>REC Ltd</t>
+          <t xml:space="preserve">Reliance Industries Ltd
+</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4595,107 +4588,107 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>REC is a Central Public Sector Undertaking under the Ministry of Power involved in financing projects in the complete power sector value chain from generation to distribution. [1]</t>
+          <t xml:space="preserve">Reliance was founded by Dhirubhai Ambani and is now promoted and managed by his elder son, Mukesh Dhirubhai Ambani. Ambani's family has about 50% shareholding in the conglomerate.
+</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://recindia.nic.in/</t>
+          <t>https://www.ril.com/</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=RECLTD</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=RELIANCE</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/rec-ltd/RECLTD/532955/</t>
+          <t>https://www.bseindia.com/stock-share-price/reliance-industries-ltd/RELIANCE/500325/</t>
         </is>
       </c>
       <c r="I77" t="n">
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>279</v>
+        <v>606</v>
       </c>
       <c r="K77" t="n">
-        <v>10</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>22.2</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/RELIANCE.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/SBILIFE.png</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reliance Industries Ltd
+          <t>SBI Life Insurance Company Ltd</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SBI Life Insurance Company Ltd is engaged in the business of life insurance and annuity. It was started as a Joint-venture between State Bank of India and BNP Paribas Cardif S.A.[1]
 </t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reliance was founded by Dhirubhai Ambani and is now promoted and managed by his elder son, Mukesh Dhirubhai Ambani. Ambani's family has about 50% shareholding in the conglomerate.
-</t>
-        </is>
-      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.ril.com/</t>
+          <t>https://www.sbilife.co.in/</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=RELIANCE</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=SBILIFE</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/reliance-industries-ltd/RELIANCE/500325/</t>
+          <t>https://www.bseindia.com/stock-share-price/sbi-life-insurance-company-ltd/SBILIFE/540719/</t>
         </is>
       </c>
       <c r="I78" t="n">
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>606</v>
+        <v>162</v>
       </c>
       <c r="K78" t="n">
-        <v>9.609999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="L78" t="n">
-        <v>9.25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/SBILIFE.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/SBIN.png</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Ltd</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4705,52 +4698,52 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">SBI Life Insurance Company Ltd is engaged in the business of life insurance and annuity. It was started as a Joint-venture between State Bank of India and BNP Paribas Cardif S.A.[1]
+          <t xml:space="preserve">State Bank of India is a Fortune 500 company. It is an Indian Multinational, Public Sector banking and financial services statutory body headquartered in Mumbai. It is the largest and oldest bank in India with over 200 years of history.[1]
 </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.sbilife.co.in/</t>
+          <t>https://sbi.co.in/</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=SBILIFE</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=SBIN</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/sbi-life-insurance-company-ltd/SBILIFE/540719/</t>
+          <t>https://www.bseindia.com/stock-share-price/state-bank-of-india/SBIN/500112/</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>162</v>
+        <v>465</v>
       </c>
       <c r="K79" t="n">
-        <v>13.2</v>
+        <v>6.16</v>
       </c>
       <c r="L79" t="n">
-        <v>12</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/SBIN.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/SHREECEM.png</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Shree Cement Ltd</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4760,52 +4753,52 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">State Bank of India is a Fortune 500 company. It is an Indian Multinational, Public Sector banking and financial services statutory body headquartered in Mumbai. It is the largest and oldest bank in India with over 200 years of history.[1]
-</t>
+          <t>Shree Cement is engaged in manufacturing and selling of cement and cement related products and is ** one of the lowest cost producers in the country. It is the 3rd largest** cement</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://sbi.co.in/</t>
+          <t>https://www.shreecement.com/</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=SBIN</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=SHREECEM</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/state-bank-of-india/SBIN/500112/</t>
+          <t>https://www.bseindia.com/stock-share-price/shree-cement-ltd/SHREECEM/500387/</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>465</v>
+        <v>5787</v>
       </c>
       <c r="K80" t="n">
-        <v>6.16</v>
+        <v>14.8</v>
       </c>
       <c r="L80" t="n">
-        <v>17.3</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/SHREECEM.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/SHRIRAMFIN.png</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Shree Cement Ltd</t>
+          <t xml:space="preserve">Shriram Finance Ltd
+</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4815,52 +4808,52 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Shree Cement is engaged in manufacturing and selling of cement and cement related products and is ** one of the lowest cost producers in the country. It is the 3rd largest** cement</t>
+          <t>Business Overview
+Shriram Transport Finance Company Ltd is a part of the SHRIRAM Group conglomerate which has a significant presence in the financing business. STFC is engaged in t</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.shreecement.com/</t>
+          <t>https://www.shriramfinance.in/</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=SHREECEM</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=SHRIRAMFIN</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/shree-cement-ltd/SHREECEM/500387/</t>
+          <t>https://www.bseindia.com/stock-share-price/shriram-finance-ltd/SHRIRAMFIN/511218/</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
-        <v>5787</v>
+        <v>279</v>
       </c>
       <c r="K81" t="n">
-        <v>14.8</v>
+        <v>11.3</v>
       </c>
       <c r="L81" t="n">
-        <v>12.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/SHRIRAMFIN.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/SIEMENS.png</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shriram Finance Ltd
-</t>
+          <t>Siemens Ltd</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4870,52 +4863,51 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Business Overview
-Shriram Transport Finance Company Ltd is a part of the SHRIRAM Group conglomerate which has a significant presence in the financing business. STFC is engaged in t</t>
+          <t>Siemens Limited offers products, integrated solutions for industrial applications for manufacturing industries, drives for process</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.shriramfinance.in/</t>
+          <t>https://www.siemens.com/in/en.html</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=SHRIRAMFIN</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=SIEMENS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/shriram-finance-ltd/SHRIRAMFIN/511218/</t>
+          <t>https://www.bseindia.com/stock-share-price/siemens-ltd/SIEMENS/500550/</t>
         </is>
       </c>
       <c r="I82" t="n">
         <v>2</v>
       </c>
       <c r="J82" t="n">
-        <v>279</v>
+        <v>431</v>
       </c>
       <c r="K82" t="n">
-        <v>11.3</v>
+        <v>25.6</v>
       </c>
       <c r="L82" t="n">
-        <v>15.9</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/SIEMENS.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/SUNPHARMA.png</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Siemens Ltd</t>
+          <t>Sun Pharmaceuticals Industries Ltd</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4925,51 +4917,52 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Siemens Limited offers products, integrated solutions for industrial applications for manufacturing industries, drives for process</t>
+          <t xml:space="preserve">Sun Pharmaceutical Industries Ltd is engaged in the business of manufacturing, developing and marketing a wide range of branded and generic formulations and Active Pharma Ingredients (APIs). The company and its subsidiaries has various manufacturing facilities spread across the world with trading and other incidental and related activities extending to global market.[1] It is the largest pharmaceutical company in India.[2]
+</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.siemens.com/in/en.html</t>
+          <t>https://sunpharma.com/</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=SIEMENS</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=SUNPHARMA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/siemens-ltd/SIEMENS/500550/</t>
+          <t>https://www.bseindia.com/stock-share-price/sun-pharmaceuticals-industries-ltd/SUNPHARMA/524715/</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
-        <v>431</v>
+        <v>288</v>
       </c>
       <c r="K83" t="n">
-        <v>25.6</v>
+        <v>17.3</v>
       </c>
       <c r="L83" t="n">
-        <v>19.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/SUNPHARMA.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/TATACONSUM.png</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sun Pharmaceuticals Industries Ltd</t>
+          <t>Tata Consumer Products Ltd</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4979,52 +4972,52 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sun Pharmaceutical Industries Ltd is engaged in the business of manufacturing, developing and marketing a wide range of branded and generic formulations and Active Pharma Ingredients (APIs). The company and its subsidiaries has various manufacturing facilities spread across the world with trading and other incidental and related activities extending to global market.[1] It is the largest pharmaceutical company in India.[2]
+          <t xml:space="preserve">Tata Consumer Products Ltd. is one of the leading companies of the Tata Group, with presence in the food and beverages business in India and internationally. It is the second largest tea company globally and has significant market presence and leadership in many markets. In addition to South Asia (mainly India), it has presence in various other geographies including Canada, UK, North America, Australia, Europe, Middle East and Africa. [1]
 </t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://sunpharma.com/</t>
+          <t>https://www.tataconsumer.com/</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=SUNPHARMA</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=TATACONSUM</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/sun-pharmaceuticals-industries-ltd/SUNPHARMA/524715/</t>
+          <t>https://www.bseindia.com/stock-share-price/tata-consumer-products-ltd/TATACONSUM/500800/</t>
         </is>
       </c>
       <c r="I84" t="n">
         <v>1</v>
       </c>
       <c r="J84" t="n">
-        <v>288</v>
+        <v>193</v>
       </c>
       <c r="K84" t="n">
-        <v>17.3</v>
+        <v>10.6</v>
       </c>
       <c r="L84" t="n">
-        <v>16.7</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/TATACONSUM.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/TATAMOTORS.png</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd</t>
+          <t>Tata Motors Ltd</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5033,174 +5026,119 @@
         </is>
       </c>
       <c r="E85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tata Consumer Products Ltd. is one of the leading companies of the Tata Group, with presence in the food and beverages business in India and internationally. It is the second largest tea company globally and has significant market presence and leadership in many markets. In addition to South Asia (mainly India), it has presence in various other geographies including Canada, UK, North America, Australia, Europe, Middle East and Africa. [1]
-</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>https://www.tataconsumer.com/</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=TATACONSUM</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>https://www.bseindia.com/stock-share-price/tata-consumer-products-ltd/TATACONSUM/500800/</t>
-        </is>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" t="n">
-        <v>193</v>
-      </c>
-      <c r="K85" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="L85" t="n">
-        <v>8.32</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>TATAMOTORS</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/TATAMOTORS.png</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Tata Motors Ltd</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
         <is>
           <t xml:space="preserve">Tata Motors Group is a leading global automobile manufacturer. Part of the illustrious multi-national conglomerate, the Tata group, it offers a wide and diverse portfolio of cars, sports utility vehicles, trucks, buses and defence vehicles to the world.
 It has operations in India, the UK, South Korea, South Africa, China, Brazil, Austria and Slovakia through a strong global network of subsidiaries, associate companies and Joint Ventures (JVs), including Jaguar Land Rover in the UK and Tata Daewoo in South Korea. 
 </t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://www.tatamotors.com/</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=TATAMOTORS</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.bseindia.com/stock-share-price/tata-motors-ltd/TATAMOTORS/500570/</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>2</v>
+      </c>
+      <c r="J85" t="n">
+        <v>275</v>
+      </c>
+      <c r="K85" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://mkt.in/static/mkt-icons/nifty100/TATAPOWER.png</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tata Power Company Ltd
+</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tata Power Company Ltd is primarily involved in the business of the generation, transmission and distribution of electricity. It aims to produce electricity completely through renewable sources. It also manufactures solar roofs and plans to build 1 lakh ev charging stations by 2025[1] The company is India's largest vertically-integrated power company.
+</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.tatamotors.com/</t>
+          <t>https://www.tatapower.com/</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=TATAMOTORS</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=TATAPOWER</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/tata-motors-ltd/TATAMOTORS/500570/</t>
+          <t>https://www.bseindia.com/stock-share-price/tata-power-company-ltd/TATAPOWER/500400/</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
-        <v>275</v>
+        <v>105</v>
       </c>
       <c r="K86" t="n">
-        <v>20.1</v>
+        <v>11.1</v>
       </c>
       <c r="L86" t="n">
-        <v>49.4</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/TATAPOWER.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/TATASTEEL.png</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tata Power Company Ltd
-</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tata Power Company Ltd is primarily involved in the business of the generation, transmission and distribution of electricity. It aims to produce electricity completely through renewable sources. It also manufactures solar roofs and plans to build 1 lakh ev charging stations by 2025[1] The company is India's largest vertically-integrated power company.
-</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>https://www.tatapower.com/</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=TATAPOWER</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>https://www.bseindia.com/stock-share-price/tata-power-company-ltd/TATAPOWER/500400/</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" t="n">
-        <v>105</v>
-      </c>
-      <c r="K87" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L87" t="n">
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/TATASTEEL.png</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
         <is>
           <t xml:space="preserve">Tata Steel Ltd
 </t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t xml:space="preserve">Tata Steel Ltd is Asia's first integrated private steel company setup in 1907.
 The company has presence across the entire value chain of steel manufacturing from mining and processing iron ore and coal to producing and distributing finished products.
@@ -5208,102 +5146,157 @@
 </t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://www.tatasteel.com/</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=TATASTEEL</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.bseindia.com/stock-share-price/tata-steel-ltd/TATASTEEL/500470/</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="n">
+        <v>72</v>
+      </c>
+      <c r="K87" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="L87" t="n">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://images.5paisa.com/MarketIcons/TCS.png</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services Ltd</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/chart/?symbol=NSE%3ATCS</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services is the flagship company and a part of Tata group. It is an IT services, consulting and business solutions organization that has been partnering with many of the world's largest businesses in their transformation journeys for over 50 years. TCS offers a consulting-led, cognitive powered, integrated portfolio of business, technology and engineering services and solutions.</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.tatasteel.com/</t>
+          <t>https://www.tcs.com/</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=TATASTEEL</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=TCS</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/tata-steel-ltd/TATASTEEL/500470/</t>
+          <t>https://www.bseindia.com/stock-share-price/tata-consultancy-services-ltd/TCS/532540/</t>
         </is>
       </c>
       <c r="I88" t="n">
         <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>72</v>
+        <v>281</v>
       </c>
       <c r="K88" t="n">
-        <v>7.02</v>
+        <v>64.3</v>
       </c>
       <c r="L88" t="n">
-        <v>6.55</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://images.5paisa.com/MarketIcons/TCS.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/TECHM.png</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd</t>
+          <t>Tech Mahindra Ltd</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/chart/?symbol=NSE%3ATCS</t>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services is the flagship company and a part of Tata group. It is an IT services, consulting and business solutions organization that has been partnering with many of the world's largest businesses in their transformation journeys for over 50 years. TCS offers a consulting-led, cognitive powered, integrated portfolio of business, technology and engineering services and solutions.</t>
+          <t>Tech Mahindra Ltd provides comprehensive range of IT services, including IT enabled service, application development and</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.tcs.com/</t>
+          <t>https://www.techmahindra.com/</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=TCS</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=TECHM</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/tata-consultancy-services-ltd/TCS/532540/</t>
+          <t>https://www.bseindia.com/stock-share-price/tech-mahindra-ltd/TECHM/532755/</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J89" t="n">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="K89" t="n">
-        <v>64.3</v>
+        <v>11.9</v>
       </c>
       <c r="L89" t="n">
-        <v>0.52</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/TECHM.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/TITAN.png</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tech Mahindra Ltd</t>
+          <t xml:space="preserve">Titan Company Ltd
+</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5313,52 +5306,52 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tech Mahindra Ltd provides comprehensive range of IT services, including IT enabled service, application development and</t>
+          <t xml:space="preserve">Titan Company Ltd is among India's most respected lifestyle companies. It has established leadership positions in the Watches, Jewellery and Eyewear categories led by its trusted brands and differentiated customer experience. It was founded in 1984 as a joint-venture between TATA Group and Tamilnadu Industrial Development Corporation (TIDCO). [1]
+</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.techmahindra.com/</t>
+          <t>https://www.titancompany.in/</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=TECHM</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=TITAN</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/tech-mahindra-ltd/TECHM/532755/</t>
+          <t>https://www.bseindia.com/stock-share-price/titan-company-ltd/TITAN/500114/</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>270</v>
+        <v>110</v>
       </c>
       <c r="K90" t="n">
-        <v>11.9</v>
+        <v>22.7</v>
       </c>
       <c r="L90" t="n">
-        <v>8.630000000000001</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/TITAN.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/TORNTPHARM.png</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titan Company Ltd
-</t>
+          <t>Torrent Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5367,109 +5360,109 @@
         </is>
       </c>
       <c r="E91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Titan Company Ltd is among India's most respected lifestyle companies. It has established leadership positions in the Watches, Jewellery and Eyewear categories led by its trusted brands and differentiated customer experience. It was founded in 1984 as a joint-venture between TATA Group and Tamilnadu Industrial Development Corporation (TIDCO). [1]
-</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>https://www.titancompany.in/</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=TITAN</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>https://www.bseindia.com/stock-share-price/titan-company-ltd/TITAN/500114/</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" t="n">
-        <v>110</v>
-      </c>
-      <c r="K91" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="L91" t="n">
-        <v>32.9</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/TORNTPHARM.png</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Torrent Pharmaceuticals Ltd</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
         <is>
           <t xml:space="preserve">Torrent Pharmaceuticals Ltd is one of the leading Indian Pharmaceutical Company engaged in research, development, manufacturing and marketing of generic pharmaceutical formulations.
 It is the flagship company of Torrent Group which also has presence in power and city gas distribution businesses.
 </t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://www.torrentpharma.com/</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://www.bseindia.com/stock-share-price/torrent-pharmaceuticals-ltd/TORNTPHARM/500420/</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>5</v>
+      </c>
+      <c r="J91" t="n">
+        <v>222</v>
+      </c>
+      <c r="K91" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="L91" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://mkt.in/static/mkt-icons/nifty100/TRENT.png</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Trent Ltd</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trent Ltd is engaged in retailing of apparels, footwear, accessories, toys, games, food, grocery &amp; non food products through various of its retail formats/ concepts.[1]
+</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.torrentpharma.com/</t>
+          <t>https://trentlimited.com/</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=TORNTPHARM</t>
+          <t>https://www.nseindia.com/get-quotes/equity?symbol=TRENT</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.bseindia.com/stock-share-price/torrent-pharmaceuticals-ltd/TORNTPHARM/500420/</t>
+          <t>https://www.bseindia.com/stock-share-price/trent-ltd/TRENT/500251/</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="K92" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="L92" t="n">
-        <v>24.2</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/TRENT.png</t>
+          <t>https://mkt.in/static/mkt-icons/nifty100/TVSMOTOR.png</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Trent Ltd</t>
+          <t>TVS Motor Company Ltd</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5479,71 +5472,16 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trent Ltd is engaged in retailing of apparels, footwear, accessories, toys, games, food, grocery &amp; non food products through various of its retail formats/ concepts.[1]
-</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>https://trentlimited.com/</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.nseindia.com/get-quotes/equity?symbol=TRENT</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>https://www.bseindia.com/stock-share-price/trent-ltd/TRENT/500251/</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" t="n">
-        <v>132</v>
-      </c>
-      <c r="K93" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="L93" t="n">
-        <v>27.2</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>https://mkt.in/static/mkt-icons/nifty100/TVSMOTOR.png</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>TVS Motor Company Ltd</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/qGsydD2w/?symbol=NSE%3AAMBUJACEM.T0</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
           <t>'TVS Motor Company Ltd (TVSM) is engaged in manufacturing two-wheelers and its accessories</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
